--- a/Mathematics/Отладка декодера.xlsx
+++ b/Mathematics/Отладка декодера.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farad\OneDrive\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farad\source\repos\AudioDataInterface OPUS test\Mathematics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B890498-E4DB-4218-826B-5C70E0D8E9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B226415-AB0F-41F0-8F25-F42B41D0CCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>i</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>b2</t>
-  </si>
-  <si>
-    <t>7878:4613:5756:5429:4820:5353:9673:10206:9412:8977:9619:4570:9064:5114:3895:8955:4515:8182:8933:9292:4417:9249:5549:3960:8977:9923:5277:4396:9738:9989:10565:5408:10010:5756:4537:9793:10478:10359:9358</t>
   </si>
 </sst>
 </file>
@@ -320,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -366,6 +363,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,118 +451,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="38"/>
                 <c:pt idx="0">
-                  <c:v>3265</c:v>
+                  <c:v>5550</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1143</c:v>
+                  <c:v>438</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>327</c:v>
+                  <c:v>587</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2780</c:v>
+                  <c:v>4898</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2171</c:v>
+                  <c:v>5315</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>533</c:v>
+                  <c:v>4986</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4853</c:v>
+                  <c:v>358</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>794</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>435</c:v>
+                  <c:v>479</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>642</c:v>
+                  <c:v>367</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5049</c:v>
+                  <c:v>5323</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4494</c:v>
+                  <c:v>5812</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3950</c:v>
+                  <c:v>282</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1219</c:v>
+                  <c:v>803</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5060</c:v>
+                  <c:v>5316</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4440</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3667</c:v>
+                  <c:v>5873</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>751</c:v>
+                  <c:v>345</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>359</c:v>
+                  <c:v>5374</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4875</c:v>
+                  <c:v>6486</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4832</c:v>
+                  <c:v>6385</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3700</c:v>
+                  <c:v>6581</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1589</c:v>
+                  <c:v>6294</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5017</c:v>
+                  <c:v>5847</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>946</c:v>
+                  <c:v>264</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4646</c:v>
+                  <c:v>989</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>881</c:v>
+                  <c:v>5725</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5342</c:v>
+                  <c:v>294</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>251</c:v>
+                  <c:v>335</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>576</c:v>
+                  <c:v>6241</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5157</c:v>
+                  <c:v>5815</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4602</c:v>
+                  <c:v>318</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4254</c:v>
+                  <c:v>5702</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1219</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5256</c:v>
+                  <c:v>299</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>685</c:v>
+                  <c:v>6027</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>119</c:v>
+                  <c:v>6527</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1001</c:v>
+                  <c:v>1290</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -612,121 +612,121 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>7878</c:v>
+                  <c:v>3784</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4613</c:v>
+                  <c:v>9334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5756</c:v>
+                  <c:v>8896</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5429</c:v>
+                  <c:v>9483</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2649</c:v>
+                  <c:v>4585</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4820</c:v>
+                  <c:v>9900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5353</c:v>
+                  <c:v>4914</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10206</c:v>
+                  <c:v>5272</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9412</c:v>
+                  <c:v>10522</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8977</c:v>
+                  <c:v>11001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9619</c:v>
+                  <c:v>11368</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4570</c:v>
+                  <c:v>6045</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9064</c:v>
+                  <c:v>11857</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5114</c:v>
+                  <c:v>11575</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3895</c:v>
+                  <c:v>12378</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8955</c:v>
+                  <c:v>7062</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4515</c:v>
+                  <c:v>7152</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8182</c:v>
+                  <c:v>13025</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8933</c:v>
+                  <c:v>13370</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9292</c:v>
+                  <c:v>7996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4417</c:v>
+                  <c:v>14482</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9249</c:v>
+                  <c:v>8097</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5549</c:v>
+                  <c:v>14678</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3960</c:v>
+                  <c:v>8384</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8977</c:v>
+                  <c:v>14231</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9923</c:v>
+                  <c:v>14495</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5277</c:v>
+                  <c:v>15484</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4396</c:v>
+                  <c:v>9759</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9738</c:v>
+                  <c:v>10053</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9989</c:v>
+                  <c:v>9718</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>10565</c:v>
+                  <c:v>15959</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5408</c:v>
+                  <c:v>10144</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10010</c:v>
+                  <c:v>10462</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5756</c:v>
+                  <c:v>16164</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4537</c:v>
+                  <c:v>16197</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9793</c:v>
+                  <c:v>16496</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10478</c:v>
+                  <c:v>10469</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10359</c:v>
+                  <c:v>16996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9358</c:v>
+                  <c:v>15706</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -782,118 +782,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>2564.3286376428396</c:v>
+                  <c:v>3309.4984857941954</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2569.2155676137818</c:v>
+                  <c:v>3313.9608720528308</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2574.1024975847231</c:v>
+                  <c:v>3318.4232583114663</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2578.9894275556653</c:v>
+                  <c:v>3322.8856445701012</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2583.8763575266066</c:v>
+                  <c:v>3327.3480308287362</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2588.7632874975488</c:v>
+                  <c:v>3331.8104170873721</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2593.6502174684906</c:v>
+                  <c:v>3336.2728033460071</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2598.5371474394324</c:v>
+                  <c:v>3340.7351896046421</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2603.4240774103746</c:v>
+                  <c:v>3345.1975758632775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2608.3110073813159</c:v>
+                  <c:v>3349.6599621219129</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2613.1979373522581</c:v>
+                  <c:v>3354.1223483805479</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2618.0848673231994</c:v>
+                  <c:v>3358.5847346391834</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2622.9717972941417</c:v>
+                  <c:v>3363.0471208978183</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2627.858727265083</c:v>
+                  <c:v>3367.5095071564538</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2632.7456572360252</c:v>
+                  <c:v>3371.9718934150887</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2637.6325872069665</c:v>
+                  <c:v>3376.4342796737237</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2642.5195171779087</c:v>
+                  <c:v>3380.8966659323596</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2647.4064471488505</c:v>
+                  <c:v>3385.3590521909946</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2652.2933771197922</c:v>
+                  <c:v>3389.8214384496296</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2657.180307090734</c:v>
+                  <c:v>3394.283824708265</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2662.0672370616758</c:v>
+                  <c:v>3398.7462109669004</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2666.9541670326175</c:v>
+                  <c:v>3403.2085972255354</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2671.8410970035593</c:v>
+                  <c:v>3407.6709834841704</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2676.7280269745011</c:v>
+                  <c:v>3412.1333697428058</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2681.6149569454428</c:v>
+                  <c:v>3416.5957560014413</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2686.5018869163846</c:v>
+                  <c:v>3421.0581422600762</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2691.3888168873264</c:v>
+                  <c:v>3425.5205285187112</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2696.2757468582686</c:v>
+                  <c:v>3429.9829147773471</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2701.1626768292103</c:v>
+                  <c:v>3434.4453010359821</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2706.0496068001521</c:v>
+                  <c:v>3438.9076872946171</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2710.9365367710939</c:v>
+                  <c:v>3443.3700735532525</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2715.8234667420356</c:v>
+                  <c:v>3447.8324598118879</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2720.7103967129774</c:v>
+                  <c:v>3452.2948460705229</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2725.5973266839192</c:v>
+                  <c:v>3456.7572323291579</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2730.4842566548609</c:v>
+                  <c:v>3461.2196185877933</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2735.3711866258027</c:v>
+                  <c:v>3465.6820048464288</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2740.2581165967445</c:v>
+                  <c:v>3470.1443911050637</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2745.1450465676862</c:v>
+                  <c:v>3474.6067773636992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -942,118 +942,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>3445.8164089248467</c:v>
+                  <c:v>5384.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1314.0425489829622</c:v>
+                  <c:v>272.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>488.2686890410796</c:v>
+                  <c:v>421.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2931.4948290991952</c:v>
+                  <c:v>4732.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2312.7209691573125</c:v>
+                  <c:v>5149.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>664.9471092154281</c:v>
+                  <c:v>4820.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4975.1732492735446</c:v>
+                  <c:v>192.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>906.39938933166104</c:v>
+                  <c:v>5084.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>537.6255293897766</c:v>
+                  <c:v>313.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>734.85166944789398</c:v>
+                  <c:v>201.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5132.0778095060095</c:v>
+                  <c:v>5157.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4567.3039495641269</c:v>
+                  <c:v>5646.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4013.5300896222425</c:v>
+                  <c:v>116.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1272.7562296803599</c:v>
+                  <c:v>637.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5103.9823697384754</c:v>
+                  <c:v>5150.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4474.2085097965928</c:v>
+                  <c:v>-75.108291569503763</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3691.4346498547084</c:v>
+                  <c:v>5707.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>765.66078991282484</c:v>
+                  <c:v>179.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>363.88692997094131</c:v>
+                  <c:v>5208.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4870.1130700290578</c:v>
+                  <c:v>6320.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4817.3392100871743</c:v>
+                  <c:v>6219.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3675.5653501452907</c:v>
+                  <c:v>6415.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1554.7914902034072</c:v>
+                  <c:v>6128.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4973.0176302615237</c:v>
+                  <c:v>5681.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>892.24377031964013</c:v>
+                  <c:v>98.891708430496237</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4582.4699103777566</c:v>
+                  <c:v>823.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>807.69605043587308</c:v>
+                  <c:v>5559.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5258.9221904939886</c:v>
+                  <c:v>128.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>158.14833055210511</c:v>
+                  <c:v>169.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>473.37447061022158</c:v>
+                  <c:v>6075.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5044.600610668338</c:v>
+                  <c:v>5649.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4479.8267507264545</c:v>
+                  <c:v>152.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4122.052890784571</c:v>
+                  <c:v>5536.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1077.2790308426875</c:v>
+                  <c:v>-132.10829156950376</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5104.5051709008039</c:v>
+                  <c:v>133.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>523.7313109589204</c:v>
+                  <c:v>5861.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-52.042548982963126</c:v>
+                  <c:v>6361.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>820.18359107515334</c:v>
+                  <c:v>1124.8917084304962</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1129,118 +1129,118 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="39"/>
                       <c:pt idx="0">
-                        <c:v>3265</c:v>
+                        <c:v>5550</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>1138.1130700290578</c:v>
+                        <c:v>433.53761374136457</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>317.22614005811647</c:v>
+                        <c:v>578.07522748272913</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>2765.3392100871743</c:v>
+                        <c:v>4884.6128412240942</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>2151.4522801162329</c:v>
+                        <c:v>5297.1504549654592</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>508.56535014529072</c:v>
+                        <c:v>4963.6880687068233</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>4823.6784201743485</c:v>
+                        <c:v>331.22568244818831</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>759.79149020340719</c:v>
+                        <c:v>5218.7632961895533</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>395.90456023246497</c:v>
+                        <c:v>443.3009099309179</c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v>598.01763026152366</c:v>
+                        <c:v>326.83852367228246</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>5000.1307002905814</c:v>
+                        <c:v>5278.3761374136475</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>4440.2437703196401</c:v>
+                        <c:v>5762.9137511550125</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>3891.3568403486979</c:v>
+                        <c:v>228.45136489637707</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>1155.4699103777566</c:v>
+                        <c:v>744.98897863774164</c:v>
                       </c:pt>
                       <c:pt idx="14">
-                        <c:v>4991.5829804068144</c:v>
+                        <c:v>5253.5265923791067</c:v>
                       </c:pt>
                       <c:pt idx="15">
-                        <c:v>4366.6960504358731</c:v>
+                        <c:v>23.064206120471681</c:v>
                       </c:pt>
                       <c:pt idx="16">
-                        <c:v>3588.8091204649309</c:v>
+                        <c:v>5801.6018198618358</c:v>
                       </c:pt>
                       <c:pt idx="17">
-                        <c:v>667.92219049398909</c:v>
+                        <c:v>269.13943360320081</c:v>
                       </c:pt>
                       <c:pt idx="18">
-                        <c:v>271.03526052304733</c:v>
+                        <c:v>5293.6770473445658</c:v>
                       </c:pt>
                       <c:pt idx="19">
-                        <c:v>4782.1483305521051</c:v>
+                        <c:v>6401.2146610859309</c:v>
                       </c:pt>
                       <c:pt idx="20">
-                        <c:v>4734.2614005811638</c:v>
+                        <c:v>6295.752274827295</c:v>
                       </c:pt>
                       <c:pt idx="21">
-                        <c:v>3597.374470610222</c:v>
+                        <c:v>6487.28988856866</c:v>
                       </c:pt>
                       <c:pt idx="22">
-                        <c:v>1481.4875406392803</c:v>
+                        <c:v>6195.827502310025</c:v>
                       </c:pt>
                       <c:pt idx="23">
-                        <c:v>4904.600610668338</c:v>
+                        <c:v>5744.3651160513891</c:v>
                       </c:pt>
                       <c:pt idx="24">
-                        <c:v>828.71368069739674</c:v>
+                        <c:v>156.90272979275414</c:v>
                       </c:pt>
                       <c:pt idx="25">
-                        <c:v>4523.8267507264554</c:v>
+                        <c:v>877.44034353411917</c:v>
                       </c:pt>
                       <c:pt idx="26">
-                        <c:v>753.93982075551321</c:v>
+                        <c:v>5608.9779572754842</c:v>
                       </c:pt>
                       <c:pt idx="27">
-                        <c:v>5210.052890784571</c:v>
+                        <c:v>173.5155710168483</c:v>
                       </c:pt>
                       <c:pt idx="28">
-                        <c:v>114.16596081362923</c:v>
+                        <c:v>210.05318475821332</c:v>
                       </c:pt>
                       <c:pt idx="29">
-                        <c:v>434.27903084268746</c:v>
+                        <c:v>6111.5907984995783</c:v>
                       </c:pt>
                       <c:pt idx="30">
-                        <c:v>5010.3921008717462</c:v>
+                        <c:v>5681.1284122409434</c:v>
                       </c:pt>
                       <c:pt idx="31">
-                        <c:v>4450.5051709008039</c:v>
+                        <c:v>179.66602598230747</c:v>
                       </c:pt>
                       <c:pt idx="32">
-                        <c:v>4097.6182409298617</c:v>
+                        <c:v>5559.2036397236725</c:v>
                       </c:pt>
                       <c:pt idx="33">
-                        <c:v>1057.7313109589204</c:v>
+                        <c:v>-114.25874653496248</c:v>
                       </c:pt>
                       <c:pt idx="34">
-                        <c:v>5089.8443809879791</c:v>
+                        <c:v>147.27886720640208</c:v>
                       </c:pt>
                       <c:pt idx="35">
-                        <c:v>513.95745101703687</c:v>
+                        <c:v>5870.8164809477666</c:v>
                       </c:pt>
                       <c:pt idx="36">
-                        <c:v>-56.929478953904891</c:v>
+                        <c:v>6366.3540946891317</c:v>
                       </c:pt>
                       <c:pt idx="37">
-                        <c:v>820.18359107515334</c:v>
+                        <c:v>1124.8917084304962</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1562,118 +1562,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>5258.9221904939886</c:v>
+                  <c:v>6829.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5132.0778095060095</c:v>
+                  <c:v>6616.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5104.5051709008039</c:v>
+                  <c:v>6438.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5103.9823697384754</c:v>
+                  <c:v>6384.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5044.600610668338</c:v>
+                  <c:v>6293.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4975.1732492735446</c:v>
+                  <c:v>6261.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4973.0176302615237</c:v>
+                  <c:v>6124.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4870.1130700290578</c:v>
+                  <c:v>5946.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4817.3392100871743</c:v>
+                  <c:v>5923.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4582.4699103777566</c:v>
+                  <c:v>5852.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4567.3039495641269</c:v>
+                  <c:v>5838.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4479.8267507264545</c:v>
+                  <c:v>5805.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4474.2085097965928</c:v>
+                  <c:v>5611.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4122.052890784571</c:v>
+                  <c:v>5370.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4013.5300896222425</c:v>
+                  <c:v>5090.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3691.4346498547084</c:v>
+                  <c:v>5015.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3675.5653501452907</c:v>
+                  <c:v>1445.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3445.8164089248467</c:v>
+                  <c:v>1079.319435865018</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2931.4948290991952</c:v>
+                  <c:v>924.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2312.7209691573125</c:v>
+                  <c:v>924.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1554.7914902034072</c:v>
+                  <c:v>845.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1314.0425489829622</c:v>
+                  <c:v>791.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1272.7562296803599</c:v>
+                  <c:v>690.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1077.2790308426875</c:v>
+                  <c:v>662.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>906.39938933166104</c:v>
+                  <c:v>634.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>892.24377031964013</c:v>
+                  <c:v>592.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>820.18359107515334</c:v>
+                  <c:v>561.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>807.69605043587308</c:v>
+                  <c:v>540.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>765.66078991282484</c:v>
+                  <c:v>526.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>734.85166944789398</c:v>
+                  <c:v>516.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>664.9471092154281</c:v>
+                  <c:v>500.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>537.6255293897766</c:v>
+                  <c:v>491.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>523.7313109589204</c:v>
+                  <c:v>488.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>488.2686890410796</c:v>
+                  <c:v>472.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>473.37447061022158</c:v>
+                  <c:v>451.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>363.88692997094131</c:v>
+                  <c:v>444.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>158.14833055210511</c:v>
+                  <c:v>428.31943586501802</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-52.042548982963126</c:v>
+                  <c:v>372.31943586501802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1722,115 +1722,115 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>126.84438098797909</c:v>
+                  <c:v>213</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.572638605205611</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5228011623285056</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>59.381759070137377</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>69.427361394793479</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.1556190120209067</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>102.90456023246588</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.773859941883529</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>234.86929970941765</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.165960813629681</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.477198837672404</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.6182409298617131</c:v>
+                  <c:v>194</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>352.15561901202182</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>108.52280116232851</c:v>
+                  <c:v>280</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>322.09543976753412</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15.869299709417646</c:v>
+                  <c:v>3570</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>229.74894122044407</c:v>
+                  <c:v>366</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>514.3215798256515</c:v>
+                  <c:v>155</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>618.77385994188262</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>757.92947895390535</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>240.74894122044498</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>41.286319302602351</c:v>
+                  <c:v>101</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>195.4771988376724</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>170.87964151102642</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>14.155619012020907</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>72.06017924448679</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12.487540639280269</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>42.035260523048237</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>30.809120464930857</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>69.904560232465883</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>127.3215798256515</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>13.894218430856199</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>35.462621917840806</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>14.894218430858018</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>109.48754063928027</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>205.7385994188362</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>210.19087953506823</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2564,118 +2564,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>3445.8164089248467</c:v>
+                  <c:v>5384.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1314.0425489829622</c:v>
+                  <c:v>272.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>488.2686890410796</c:v>
+                  <c:v>421.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2931.4948290991952</c:v>
+                  <c:v>4732.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2312.7209691573125</c:v>
+                  <c:v>5149.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>664.9471092154281</c:v>
+                  <c:v>4820.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4975.1732492735446</c:v>
+                  <c:v>192.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>906.39938933166104</c:v>
+                  <c:v>5084.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>537.6255293897766</c:v>
+                  <c:v>313.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>734.85166944789398</c:v>
+                  <c:v>201.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5132.0778095060095</c:v>
+                  <c:v>5157.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4567.3039495641269</c:v>
+                  <c:v>5646.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4013.5300896222425</c:v>
+                  <c:v>116.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1272.7562296803599</c:v>
+                  <c:v>637.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5103.9823697384754</c:v>
+                  <c:v>5150.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4474.2085097965928</c:v>
+                  <c:v>-75.108291569503763</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3691.4346498547084</c:v>
+                  <c:v>5707.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>765.66078991282484</c:v>
+                  <c:v>179.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>363.88692997094131</c:v>
+                  <c:v>5208.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4870.1130700290578</c:v>
+                  <c:v>6320.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4817.3392100871743</c:v>
+                  <c:v>6219.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3675.5653501452907</c:v>
+                  <c:v>6415.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1554.7914902034072</c:v>
+                  <c:v>6128.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4973.0176302615237</c:v>
+                  <c:v>5681.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>892.24377031964013</c:v>
+                  <c:v>98.891708430496237</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4582.4699103777566</c:v>
+                  <c:v>823.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>807.69605043587308</c:v>
+                  <c:v>5559.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5258.9221904939886</c:v>
+                  <c:v>128.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>158.14833055210511</c:v>
+                  <c:v>169.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>473.37447061022158</c:v>
+                  <c:v>6075.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5044.600610668338</c:v>
+                  <c:v>5649.8917084304967</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4479.8267507264545</c:v>
+                  <c:v>152.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4122.052890784571</c:v>
+                  <c:v>5536.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1077.2790308426875</c:v>
+                  <c:v>-132.10829156950376</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5104.5051709008039</c:v>
+                  <c:v>133.89170843049624</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>523.7313109589204</c:v>
+                  <c:v>5861.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-52.042548982963126</c:v>
+                  <c:v>6361.8917084304958</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>820.18359107515334</c:v>
+                  <c:v>1124.8917084304962</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2721,118 +2721,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="38"/>
                 <c:pt idx="0">
-                  <c:v>3265</c:v>
+                  <c:v>5550</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1143</c:v>
+                  <c:v>438</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>327</c:v>
+                  <c:v>587</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2780</c:v>
+                  <c:v>4898</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2171</c:v>
+                  <c:v>5315</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>533</c:v>
+                  <c:v>4986</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4853</c:v>
+                  <c:v>358</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>794</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>435</c:v>
+                  <c:v>479</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>642</c:v>
+                  <c:v>367</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5049</c:v>
+                  <c:v>5323</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4494</c:v>
+                  <c:v>5812</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3950</c:v>
+                  <c:v>282</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1219</c:v>
+                  <c:v>803</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5060</c:v>
+                  <c:v>5316</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4440</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3667</c:v>
+                  <c:v>5873</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>751</c:v>
+                  <c:v>345</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>359</c:v>
+                  <c:v>5374</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4875</c:v>
+                  <c:v>6486</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4832</c:v>
+                  <c:v>6385</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3700</c:v>
+                  <c:v>6581</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1589</c:v>
+                  <c:v>6294</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5017</c:v>
+                  <c:v>5847</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>946</c:v>
+                  <c:v>264</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4646</c:v>
+                  <c:v>989</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>881</c:v>
+                  <c:v>5725</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5342</c:v>
+                  <c:v>294</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>251</c:v>
+                  <c:v>335</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>576</c:v>
+                  <c:v>6241</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5157</c:v>
+                  <c:v>5815</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4602</c:v>
+                  <c:v>318</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4254</c:v>
+                  <c:v>5702</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1219</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5256</c:v>
+                  <c:v>299</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>685</c:v>
+                  <c:v>6027</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>119</c:v>
+                  <c:v>6527</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1001</c:v>
+                  <c:v>1290</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3133,7 +3133,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -3142,10 +3142,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3160,7 +3160,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -3169,7 +3169,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1</c:v>
@@ -3178,7 +3178,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>1</c:v>
@@ -3190,7 +3190,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>1</c:v>
@@ -3199,25 +3199,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>1</c:v>
@@ -3226,13 +3226,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="35">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
@@ -3527,115 +3527,115 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>16089.496988223593</c:v>
+                  <c:v>45369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>760.25039965327483</c:v>
+                  <c:v>31684</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.27332105533203643</c:v>
+                  <c:v>2916</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3526.1933102638427</c:v>
+                  <c:v>8281</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4820.15851024326</c:v>
+                  <c:v>1024</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.6466933249859901</c:v>
+                  <c:v>18769</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10589.348516637199</c:v>
+                  <c:v>31684</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2785.0802931655389</c:v>
+                  <c:v>529</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>55163.587945992251</c:v>
+                  <c:v>5041</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>230.00636740055106</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7652.2603164856746</c:v>
+                  <c:v>1089</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>31.564631145973408</c:v>
+                  <c:v>37636</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>124013.58000174027</c:v>
+                  <c:v>58081</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11777.19837211829</c:v>
+                  <c:v>78400</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>103745.4723190412</c:v>
+                  <c:v>5625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>251.83467326732298</c:v>
+                  <c:v>12744900</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52784.575991915066</c:v>
+                  <c:v>133956</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>264526.687474354</c:v>
+                  <c:v>24025</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>382881.08974737657</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>574457.09506733844</c:v>
+                  <c:v>6241</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>57960.05269876527</c:v>
+                  <c:v>2916</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1704.5601615564356</c:v>
+                  <c:v>10201</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>38211.335265422917</c:v>
+                  <c:v>784</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>29199.851882936902</c:v>
+                  <c:v>784</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>200.38154961348775</c:v>
+                  <c:v>1764</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5192.6694327475643</c:v>
+                  <c:v>961</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>155.93867121767627</c:v>
+                  <c:v>441</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1766.9631272405375</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>949.20190382262126</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4886.647541294451</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>16210.784689299746</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>193.0493058043441</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1257.5975532877233</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>221.83774266611067</c:v>
+                  <c:v>441</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>11987.521555238049</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>42328.371290824347</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>44180.205839725568</c:v>
+                  <c:v>3136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7596,8 +7596,11 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <f ca="1">RANDBETWEEN(9500,10500)</f>
-        <v>9890</v>
+        <v>3784</v>
+      </c>
+      <c r="B4" s="1">
+        <f>A4+H4</f>
+        <v>3784</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -7606,25 +7609,28 @@
         <v>1</v>
       </c>
       <c r="E4" s="8">
-        <f>K90</f>
-        <v>7878</v>
+        <v>3784</v>
       </c>
       <c r="F4" s="1">
         <f>E94-((B94-$B$94)/1)</f>
-        <v>3265</v>
+        <v>5550</v>
       </c>
       <c r="G4" s="1">
-        <f>F4+(($B$131-B94)/1)</f>
-        <v>3445.8164089248467</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>22</v>
-      </c>
+        <f>F4-(($B$131-B94)/1)</f>
+        <v>5384.8917084304958</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <f t="shared" ref="A5:A42" ca="1" si="0">RANDBETWEEN(9500,10500)</f>
-        <v>9512</v>
+        <v>9164</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" ref="B5:B42" si="0">A5+H5</f>
+        <v>9334</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -7633,23 +7639,28 @@
         <v>1</v>
       </c>
       <c r="E5" s="8">
-        <f>L90</f>
-        <v>4613</v>
+        <v>9334</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ref="F5:F41" si="1">E95-((B95-$B$94)/1)</f>
-        <v>1138.1130700290578</v>
+        <v>433.53761374136457</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5:G40" si="2">F5+(($B$131-B95)/1)</f>
-        <v>1314.0425489829622</v>
+        <f t="shared" ref="G5:G41" si="2">F5-(($B$131-B95)/1)</f>
+        <v>272.89170843049624</v>
+      </c>
+      <c r="H5" s="1">
+        <v>170</v>
       </c>
       <c r="J5" s="13"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10236</v>
+        <v>8556</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>8896</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -7658,23 +7669,28 @@
         <v>0</v>
       </c>
       <c r="E6" s="8">
-        <f>M90</f>
-        <v>5756</v>
+        <v>8896</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="1"/>
-        <v>317.22614005811647</v>
+        <v>578.07522748272913</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="2"/>
-        <v>488.2686890410796</v>
+        <v>421.89170843049624</v>
+      </c>
+      <c r="H6" s="1">
+        <v>340</v>
       </c>
       <c r="J6" s="13"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10423</v>
+        <v>8973</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>9483</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -7683,23 +7699,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="8">
-        <f>N90</f>
-        <v>5429</v>
+        <v>9483</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
-        <v>2765.3392100871743</v>
+        <v>4884.6128412240942</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="2"/>
-        <v>2931.4948290991952</v>
+        <v>4732.8917084304958</v>
+      </c>
+      <c r="H7" s="1">
+        <v>510</v>
       </c>
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9861</v>
+        <v>3905</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>4585</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -7708,22 +7729,28 @@
         <v>1</v>
       </c>
       <c r="E8" s="8">
-        <v>2649</v>
+        <v>4585</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="1"/>
-        <v>2151.4522801162329</v>
+        <v>5297.1504549654592</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="2"/>
-        <v>2312.7209691573125</v>
+        <v>5149.8917084304958</v>
+      </c>
+      <c r="H8" s="1">
+        <v>680</v>
       </c>
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10467</v>
+        <v>9050</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>9900</v>
       </c>
       <c r="C9" s="1">
         <v>6</v>
@@ -7732,23 +7759,28 @@
         <v>0</v>
       </c>
       <c r="E9" s="8">
-        <f>O90</f>
-        <v>4820</v>
+        <v>9900</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="1"/>
-        <v>508.56535014529072</v>
+        <v>4963.6880687068233</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" si="2"/>
-        <v>664.9471092154281</v>
+        <v>4820.8917084304958</v>
+      </c>
+      <c r="H9" s="1">
+        <v>850</v>
       </c>
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10423</v>
+        <v>3894</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>4914</v>
       </c>
       <c r="C10" s="1">
         <v>7</v>
@@ -7757,23 +7789,28 @@
         <v>1</v>
       </c>
       <c r="E10" s="8">
-        <f>P90</f>
-        <v>5353</v>
+        <v>4914</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="1"/>
-        <v>4823.6784201743485</v>
+        <v>331.22568244818831</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="2"/>
-        <v>4975.1732492735446</v>
+        <v>192.89170843049624</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1020</v>
       </c>
       <c r="J10" s="13"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9631</v>
+        <v>4082</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>5272</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -7782,23 +7819,28 @@
         <v>1</v>
       </c>
       <c r="E11" s="8">
-        <f>R90</f>
-        <v>10206</v>
+        <v>5272</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="1"/>
-        <v>759.79149020340719</v>
+        <v>5218.7632961895533</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="2"/>
-        <v>906.39938933166104</v>
+        <v>5084.8917084304958</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1190</v>
       </c>
       <c r="J11" s="13"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9885</v>
+        <v>9162</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>10522</v>
       </c>
       <c r="C12" s="1">
         <v>9</v>
@@ -7807,23 +7849,28 @@
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f>S90</f>
-        <v>9412</v>
+        <v>10522</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="1"/>
-        <v>395.90456023246497</v>
+        <v>443.3009099309179</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="2"/>
-        <v>537.6255293897766</v>
+        <v>313.89170843049624</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1360</v>
       </c>
       <c r="J12" s="13"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9740</v>
+        <v>9471</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>11001</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -7832,23 +7879,28 @@
         <v>1</v>
       </c>
       <c r="E13" s="8">
-        <f>T90</f>
-        <v>8977</v>
+        <v>11001</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" si="1"/>
-        <v>598.01763026152366</v>
+        <v>326.83852367228246</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" si="2"/>
-        <v>734.85166944789398</v>
+        <v>201.89170843049624</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1530</v>
       </c>
       <c r="J13" s="13"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10476</v>
+        <v>9668</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>11368</v>
       </c>
       <c r="C14" s="1">
         <v>11</v>
@@ -7857,23 +7909,28 @@
         <v>0</v>
       </c>
       <c r="E14" s="8">
-        <f>U90</f>
-        <v>9619</v>
+        <v>11368</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="1"/>
-        <v>5000.1307002905814</v>
+        <v>5278.3761374136475</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" si="2"/>
-        <v>5132.0778095060095</v>
+        <v>5157.8917084304958</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1700</v>
       </c>
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9979</v>
+        <v>4175</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>6045</v>
       </c>
       <c r="C15" s="1">
         <v>12</v>
@@ -7882,23 +7939,28 @@
         <v>1</v>
       </c>
       <c r="E15" s="8">
-        <f>V90</f>
-        <v>4570</v>
+        <v>6045</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="1"/>
-        <v>4440.2437703196401</v>
+        <v>5762.9137511550125</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="2"/>
-        <v>4567.3039495641269</v>
+        <v>5646.8917084304967</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1870</v>
       </c>
       <c r="J15" s="13"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10176</v>
+        <v>9817</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>11857</v>
       </c>
       <c r="C16" s="1">
         <v>13</v>
@@ -7907,23 +7969,28 @@
         <v>0</v>
       </c>
       <c r="E16" s="8">
-        <f>W90</f>
-        <v>9064</v>
+        <v>11857</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="1"/>
-        <v>3891.3568403486979</v>
+        <v>228.45136489637707</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>4013.5300896222425</v>
+        <v>116.89170843049624</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2040</v>
       </c>
       <c r="J16" s="13"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9622</v>
+        <v>9365</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>11575</v>
       </c>
       <c r="C17" s="1">
         <v>14</v>
@@ -7932,23 +7999,28 @@
         <v>1</v>
       </c>
       <c r="E17" s="8">
-        <f>X90</f>
-        <v>5114</v>
+        <v>11575</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="1"/>
-        <v>1155.4699103777566</v>
+        <v>744.98897863774164</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>1272.7562296803599</v>
+        <v>637.89170843049624</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2210</v>
       </c>
       <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10110</v>
+        <v>9998</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>12378</v>
       </c>
       <c r="C18" s="1">
         <v>15</v>
@@ -7957,23 +8029,28 @@
         <v>0</v>
       </c>
       <c r="E18" s="8">
-        <f>Y90</f>
-        <v>3895</v>
+        <v>12378</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="1"/>
-        <v>4991.5829804068144</v>
+        <v>5253.5265923791067</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>5103.9823697384754</v>
+        <v>5150.8917084304958</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2380</v>
       </c>
       <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10197</v>
+        <v>4512</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>7062</v>
       </c>
       <c r="C19" s="1">
         <v>16</v>
@@ -7982,23 +8059,28 @@
         <v>1</v>
       </c>
       <c r="E19" s="8">
-        <f>Z90</f>
-        <v>8955</v>
+        <v>7062</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="1"/>
-        <v>4366.6960504358731</v>
+        <v>23.064206120471681</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>4474.2085097965928</v>
+        <v>-75.108291569503763</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2550</v>
       </c>
       <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9973</v>
+        <v>4432</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>7152</v>
       </c>
       <c r="C20" s="1">
         <v>17</v>
@@ -8007,23 +8089,28 @@
         <v>1</v>
       </c>
       <c r="E20" s="8">
-        <f>AA90</f>
-        <v>4515</v>
+        <v>7152</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="1"/>
-        <v>3588.8091204649309</v>
+        <v>5801.6018198618358</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>3691.4346498547084</v>
+        <v>5707.8917084304958</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2720</v>
       </c>
       <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10433</v>
+        <v>10135</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>13025</v>
       </c>
       <c r="C21" s="1">
         <v>18</v>
@@ -8032,23 +8119,28 @@
         <v>0</v>
       </c>
       <c r="E21" s="8">
-        <f>AB90</f>
-        <v>8182</v>
+        <v>13025</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="1"/>
-        <v>667.92219049398909</v>
+        <v>269.13943360320081</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>765.66078991282484</v>
+        <v>179.89170843049624</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2890</v>
       </c>
       <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10395</v>
+        <v>10310</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>13370</v>
       </c>
       <c r="C22" s="1">
         <v>19</v>
@@ -8057,23 +8149,28 @@
         <v>1</v>
       </c>
       <c r="E22" s="8">
-        <f>AC90</f>
-        <v>8933</v>
+        <v>13370</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" si="1"/>
-        <v>271.03526052304733</v>
+        <v>5293.6770473445658</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="2"/>
-        <v>363.88692997094131</v>
+        <v>5208.8917084304958</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3060</v>
       </c>
       <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9638</v>
+        <v>4766</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>7996</v>
       </c>
       <c r="C23" s="1">
         <v>20</v>
@@ -8082,23 +8179,28 @@
         <v>0</v>
       </c>
       <c r="E23" s="8">
-        <f>AD90</f>
-        <v>9292</v>
+        <v>7996</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" si="1"/>
-        <v>4782.1483305521051</v>
+        <v>6401.2146610859309</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="2"/>
-        <v>4870.1130700290578</v>
+        <v>6320.8917084304967</v>
+      </c>
+      <c r="H23" s="1">
+        <v>3230</v>
       </c>
       <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9920</v>
+        <v>11082</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>14482</v>
       </c>
       <c r="C24" s="1">
         <v>21</v>
@@ -8107,23 +8209,28 @@
         <v>1</v>
       </c>
       <c r="E24" s="8">
-        <f>AE90</f>
-        <v>4417</v>
+        <v>14482</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" si="1"/>
-        <v>4734.2614005811638</v>
+        <v>6295.752274827295</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" si="2"/>
-        <v>4817.3392100871743</v>
+        <v>6219.8917084304958</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3400</v>
       </c>
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10255</v>
+        <v>4527</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>8097</v>
       </c>
       <c r="C25" s="1">
         <v>22</v>
@@ -8132,23 +8239,28 @@
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <f>AF90</f>
-        <v>9249</v>
+        <v>8097</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" si="1"/>
-        <v>3597.374470610222</v>
+        <v>6487.28988856866</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="2"/>
-        <v>3675.5653501452907</v>
+        <v>6415.8917084304958</v>
+      </c>
+      <c r="H25" s="1">
+        <v>3570</v>
       </c>
       <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9908</v>
+        <v>10938</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>14678</v>
       </c>
       <c r="C26" s="1">
         <v>23</v>
@@ -8157,23 +8269,28 @@
         <v>1</v>
       </c>
       <c r="E26" s="8">
-        <f>AG90</f>
-        <v>5549</v>
+        <v>14678</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" si="1"/>
-        <v>1481.4875406392803</v>
+        <v>6195.827502310025</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="2"/>
-        <v>1554.7914902034072</v>
+        <v>6128.8917084304958</v>
+      </c>
+      <c r="H26" s="1">
+        <v>3740</v>
       </c>
       <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9538</v>
+        <v>4474</v>
+      </c>
+      <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>8384</v>
       </c>
       <c r="C27" s="1">
         <v>24</v>
@@ -8182,23 +8299,28 @@
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f>AH90</f>
-        <v>3960</v>
+        <v>8384</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" si="1"/>
-        <v>4904.600610668338</v>
+        <v>5744.3651160513891</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="2"/>
-        <v>4973.0176302615237</v>
+        <v>5681.8917084304958</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3910</v>
       </c>
       <c r="J27" s="13"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9515</v>
+        <v>10151</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>14231</v>
       </c>
       <c r="C28" s="1">
         <v>25</v>
@@ -8207,23 +8329,28 @@
         <v>1</v>
       </c>
       <c r="E28" s="8">
-        <f>AI90</f>
-        <v>8977</v>
+        <v>14231</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" si="1"/>
-        <v>828.71368069739674</v>
+        <v>156.90272979275414</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="2"/>
-        <v>892.24377031964013</v>
+        <v>98.891708430496237</v>
+      </c>
+      <c r="H28" s="1">
+        <v>4080</v>
       </c>
       <c r="J28" s="13"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10124</v>
+        <v>10245</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>14495</v>
       </c>
       <c r="C29" s="1">
         <v>26</v>
@@ -8232,23 +8359,28 @@
         <v>0</v>
       </c>
       <c r="E29" s="8">
-        <f>AJ90</f>
-        <v>9923</v>
+        <v>14495</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" si="1"/>
-        <v>4523.8267507264554</v>
+        <v>877.44034353411917</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="2"/>
-        <v>4582.4699103777566</v>
+        <v>823.89170843049624</v>
+      </c>
+      <c r="H29" s="1">
+        <v>4250</v>
       </c>
       <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9792</v>
+        <v>11064</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>15484</v>
       </c>
       <c r="C30" s="1">
         <v>27</v>
@@ -8257,23 +8389,28 @@
         <v>1</v>
       </c>
       <c r="E30" s="8">
-        <f>AK90</f>
-        <v>5277</v>
+        <v>15484</v>
       </c>
       <c r="F30" s="1">
         <f t="shared" si="1"/>
-        <v>753.93982075551321</v>
+        <v>5608.9779572754842</v>
       </c>
       <c r="G30" s="1">
         <f t="shared" si="2"/>
-        <v>807.69605043587308</v>
+        <v>5559.8917084304958</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4420</v>
       </c>
       <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9998</v>
+        <v>5169</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>9759</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -8282,23 +8419,28 @@
         <v>0</v>
       </c>
       <c r="E31" s="8">
-        <f>AL90</f>
-        <v>4396</v>
+        <v>9759</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" si="1"/>
-        <v>5210.052890784571</v>
+        <v>173.5155710168483</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="2"/>
-        <v>5258.9221904939886</v>
+        <v>128.89170843049624</v>
+      </c>
+      <c r="H31" s="1">
+        <v>4590</v>
       </c>
       <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10255</v>
+        <v>5293</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>10053</v>
       </c>
       <c r="C32" s="1">
         <v>29</v>
@@ -8307,23 +8449,28 @@
         <v>1</v>
       </c>
       <c r="E32" s="8">
-        <f>AM90</f>
-        <v>9738</v>
+        <v>10053</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" si="1"/>
-        <v>114.16596081362923</v>
+        <v>210.05318475821332</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" si="2"/>
-        <v>158.14833055210511</v>
+        <v>169.89170843049624</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4760</v>
       </c>
       <c r="J32" s="13"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10498</v>
+        <v>4788</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>9718</v>
       </c>
       <c r="C33" s="1">
         <v>30</v>
@@ -8332,23 +8479,28 @@
         <v>1</v>
       </c>
       <c r="E33" s="8">
-        <f>AN90</f>
-        <v>9989</v>
+        <v>9718</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" si="1"/>
-        <v>434.27903084268746</v>
+        <v>6111.5907984995783</v>
       </c>
       <c r="G33" s="1">
         <f t="shared" si="2"/>
-        <v>473.37447061022158</v>
+        <v>6075.8917084304958</v>
+      </c>
+      <c r="H33" s="1">
+        <v>4930</v>
       </c>
       <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10028</v>
+        <v>10859</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" si="0"/>
+        <v>15959</v>
       </c>
       <c r="C34" s="1">
         <v>31</v>
@@ -8357,23 +8509,28 @@
         <v>1</v>
       </c>
       <c r="E34" s="8">
-        <f>AO90</f>
-        <v>10565</v>
+        <v>15959</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" si="1"/>
-        <v>5010.3921008717462</v>
+        <v>5681.1284122409434</v>
       </c>
       <c r="G34" s="1">
         <f t="shared" si="2"/>
-        <v>5044.600610668338</v>
+        <v>5649.8917084304967</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5100</v>
       </c>
       <c r="J34" s="13"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9818</v>
+        <v>4874</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" si="0"/>
+        <v>10144</v>
       </c>
       <c r="C35" s="1">
         <v>32</v>
@@ -8382,23 +8539,28 @@
         <v>0</v>
       </c>
       <c r="E35" s="8">
-        <f>AP90</f>
-        <v>5408</v>
+        <v>10144</v>
       </c>
       <c r="F35" s="1">
         <f t="shared" si="1"/>
-        <v>4450.5051709008039</v>
+        <v>179.66602598230747</v>
       </c>
       <c r="G35" s="1">
         <f t="shared" si="2"/>
-        <v>4479.8267507264545</v>
+        <v>152.89170843049624</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5270</v>
       </c>
       <c r="J35" s="13"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9630</v>
+        <v>5022</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" si="0"/>
+        <v>10462</v>
       </c>
       <c r="C36" s="1">
         <v>33</v>
@@ -8407,23 +8569,28 @@
         <v>1</v>
       </c>
       <c r="E36" s="8">
-        <f>AQ90</f>
-        <v>10010</v>
+        <v>10462</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" si="1"/>
-        <v>4097.6182409298617</v>
+        <v>5559.2036397236725</v>
       </c>
       <c r="G36" s="1">
         <f t="shared" si="2"/>
-        <v>4122.052890784571</v>
+        <v>5536.8917084304958</v>
+      </c>
+      <c r="H36" s="1">
+        <v>5440</v>
       </c>
       <c r="J36" s="13"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10459</v>
+        <v>10554</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" si="0"/>
+        <v>16164</v>
       </c>
       <c r="C37" s="1">
         <v>34</v>
@@ -8432,23 +8599,28 @@
         <v>1</v>
       </c>
       <c r="E37" s="8">
-        <f>AR90</f>
-        <v>5756</v>
+        <v>16164</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" si="1"/>
-        <v>1057.7313109589204</v>
+        <v>-114.25874653496248</v>
       </c>
       <c r="G37" s="1">
         <f t="shared" si="2"/>
-        <v>1077.2790308426875</v>
+        <v>-132.10829156950376</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5610</v>
       </c>
       <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10162</v>
+        <v>10417</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" si="0"/>
+        <v>16197</v>
       </c>
       <c r="C38" s="1">
         <v>35</v>
@@ -8457,23 +8629,28 @@
         <v>1</v>
       </c>
       <c r="E38" s="8">
-        <f>AS90</f>
-        <v>4537</v>
+        <v>16197</v>
       </c>
       <c r="F38" s="1">
         <f t="shared" si="1"/>
-        <v>5089.8443809879791</v>
+        <v>147.27886720640208</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" si="2"/>
-        <v>5104.5051709008039</v>
+        <v>133.89170843049624</v>
+      </c>
+      <c r="H38" s="1">
+        <v>5780</v>
       </c>
       <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9683</v>
+        <v>10546</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>16496</v>
       </c>
       <c r="C39" s="1">
         <v>36</v>
@@ -8482,23 +8659,28 @@
         <v>1</v>
       </c>
       <c r="E39" s="8">
-        <f>AT90</f>
-        <v>9793</v>
+        <v>16496</v>
       </c>
       <c r="F39" s="1">
         <f t="shared" si="1"/>
-        <v>513.95745101703687</v>
+        <v>5870.8164809477666</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="2"/>
-        <v>523.7313109589204</v>
+        <v>5861.8917084304958</v>
+      </c>
+      <c r="H39" s="1">
+        <v>5950</v>
       </c>
       <c r="J39" s="13"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>9904</v>
+        <v>4349</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>10469</v>
       </c>
       <c r="C40" s="1">
         <v>37</v>
@@ -8507,23 +8689,28 @@
         <v>1</v>
       </c>
       <c r="E40" s="8">
-        <f>AU90</f>
-        <v>10478</v>
+        <v>10469</v>
       </c>
       <c r="F40" s="1">
         <f t="shared" si="1"/>
-        <v>-56.929478953904891</v>
+        <v>6366.3540946891317</v>
       </c>
       <c r="G40" s="1">
         <f t="shared" si="2"/>
-        <v>-52.042548982963126</v>
+        <v>6361.8917084304958</v>
+      </c>
+      <c r="H40" s="1">
+        <v>6120</v>
       </c>
       <c r="J40" s="13"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10232</v>
+        <v>10706</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>16996</v>
       </c>
       <c r="C41" s="1">
         <v>38</v>
@@ -8532,23 +8719,28 @@
         <v>1</v>
       </c>
       <c r="E41" s="8">
-        <f>AV90</f>
-        <v>10359</v>
+        <v>16996</v>
       </c>
       <c r="F41" s="1">
         <f t="shared" si="1"/>
-        <v>820.18359107515334</v>
+        <v>1124.8917084304962</v>
       </c>
       <c r="G41" s="1">
-        <f>F41+(($B$131-B131)/1)</f>
-        <v>820.18359107515334</v>
+        <f t="shared" si="2"/>
+        <v>1124.8917084304962</v>
+      </c>
+      <c r="H41" s="1">
+        <v>6290</v>
       </c>
       <c r="J41" s="13"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>10093</v>
+        <v>9246</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>15706</v>
       </c>
       <c r="C42" s="1">
         <v>39</v>
@@ -8557,8 +8749,10 @@
         <v>1</v>
       </c>
       <c r="E42" s="8">
-        <f>AW90</f>
-        <v>9358</v>
+        <v>15706</v>
+      </c>
+      <c r="H42" s="1">
+        <v>6460</v>
       </c>
       <c r="J42" s="13"/>
     </row>
@@ -8593,40 +8787,40 @@
       </c>
       <c r="L46" s="12">
         <f>G4</f>
-        <v>3445.8164089248467</v>
+        <v>5384.8917084304958</v>
       </c>
       <c r="N46" s="1">
-        <v>5258.9221904939886</v>
+        <v>6829.319435865018</v>
       </c>
       <c r="P46" s="1">
         <f>N46-N47</f>
-        <v>126.84438098797909</v>
+        <v>213</v>
       </c>
       <c r="Q46" s="1">
         <f>P46^2</f>
-        <v>16089.496988223593</v>
+        <v>45369</v>
       </c>
       <c r="R46" s="10">
         <f>MAX(P46:P82)</f>
-        <v>757.92947895390535</v>
+        <v>3570</v>
       </c>
       <c r="T46" s="1">
         <v>1</v>
       </c>
       <c r="U46" s="1" t="str">
         <f>IF((E5-E4)&gt;0,"+","-")</f>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V46" s="5">
         <f>ABS(E5-E4)</f>
-        <v>3265</v>
+        <v>5550</v>
       </c>
       <c r="W46" s="6">
-        <v>2606.566667034127</v>
+        <v>6528</v>
       </c>
       <c r="X46" s="5">
         <f>ABS(E5-E4)</f>
-        <v>3265</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -8635,19 +8829,19 @@
         <v>0</v>
       </c>
       <c r="L47" s="12">
-        <f t="shared" ref="L47:N83" si="4">G5</f>
-        <v>1314.0425489829622</v>
+        <f t="shared" ref="L47:L83" si="4">G5</f>
+        <v>272.89170843049624</v>
       </c>
       <c r="N47" s="1">
-        <v>5132.0778095060095</v>
+        <v>6616.319435865018</v>
       </c>
       <c r="P47" s="1">
         <f t="shared" ref="P47:P82" si="5">N47-N48</f>
-        <v>27.572638605205611</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="1">
         <f t="shared" ref="Q47:Q82" si="6">P47^2</f>
-        <v>760.25039965327483</v>
+        <v>31684</v>
       </c>
       <c r="R47" s="8"/>
       <c r="T47" s="1">
@@ -8655,18 +8849,18 @@
       </c>
       <c r="U47" s="1" t="str">
         <f t="shared" ref="U47:U83" si="7">IF((E6-E5)&gt;0,"+","-")</f>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V47" s="5">
-        <f t="shared" ref="V47:V83" si="8">ABS(E6-E5)</f>
-        <v>1143</v>
+        <f t="shared" ref="V47:W83" si="8">ABS(E6-E5)</f>
+        <v>438</v>
       </c>
       <c r="W47" s="3">
-        <v>5512.4333329658739</v>
+        <v>6315</v>
       </c>
       <c r="X47" s="5">
         <f t="shared" ref="X47:X83" si="9">ABS(E6-E5)</f>
-        <v>1143</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
@@ -8676,18 +8870,18 @@
       </c>
       <c r="L48" s="12">
         <f t="shared" si="4"/>
-        <v>488.2686890410796</v>
+        <v>421.89170843049624</v>
       </c>
       <c r="N48" s="1">
-        <v>5104.5051709008039</v>
+        <v>6438.319435865018</v>
       </c>
       <c r="P48" s="1">
         <f t="shared" si="5"/>
-        <v>0.5228011623285056</v>
+        <v>54</v>
       </c>
       <c r="Q48" s="1">
         <f t="shared" si="6"/>
-        <v>0.27332105533203643</v>
+        <v>2916</v>
       </c>
       <c r="R48" s="8"/>
       <c r="T48" s="1">
@@ -8695,39 +8889,39 @@
       </c>
       <c r="U48" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V48" s="5">
         <f t="shared" si="8"/>
-        <v>327</v>
+        <v>587</v>
       </c>
       <c r="W48" s="3">
-        <v>5042.5666670341261</v>
+        <v>6137</v>
       </c>
       <c r="X48" s="5">
         <f t="shared" si="9"/>
-        <v>327</v>
+        <v>587</v>
       </c>
     </row>
     <row r="49" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K49" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="12">
         <f t="shared" si="4"/>
-        <v>2931.4948290991952</v>
+        <v>4732.8917084304958</v>
       </c>
       <c r="N49" s="1">
-        <v>5103.9823697384754</v>
+        <v>6384.319435865018</v>
       </c>
       <c r="P49" s="1">
         <f t="shared" si="5"/>
-        <v>59.381759070137377</v>
+        <v>91</v>
       </c>
       <c r="Q49" s="1">
         <f t="shared" si="6"/>
-        <v>3526.1933102638427</v>
+        <v>8281</v>
       </c>
       <c r="R49" s="8"/>
       <c r="T49" s="1">
@@ -8739,14 +8933,14 @@
       </c>
       <c r="V49" s="5">
         <f t="shared" si="8"/>
-        <v>2780</v>
+        <v>4898</v>
       </c>
       <c r="W49" s="3">
-        <v>4978.5666670341261</v>
+        <v>6083</v>
       </c>
       <c r="X49" s="5">
         <f t="shared" si="9"/>
-        <v>2780</v>
+        <v>4898</v>
       </c>
     </row>
     <row r="50" spans="11:24" x14ac:dyDescent="0.25">
@@ -8756,18 +8950,18 @@
       </c>
       <c r="L50" s="12">
         <f t="shared" si="4"/>
-        <v>2312.7209691573125</v>
+        <v>5149.8917084304958</v>
       </c>
       <c r="N50" s="1">
-        <v>5044.600610668338</v>
+        <v>6293.319435865018</v>
       </c>
       <c r="P50" s="1">
         <f t="shared" si="5"/>
-        <v>69.427361394793479</v>
+        <v>32</v>
       </c>
       <c r="Q50" s="1">
         <f t="shared" si="6"/>
-        <v>4820.15851024326</v>
+        <v>1024</v>
       </c>
       <c r="R50" s="8"/>
       <c r="T50" s="1">
@@ -8779,14 +8973,14 @@
       </c>
       <c r="V50" s="5">
         <f t="shared" si="8"/>
-        <v>2171</v>
+        <v>5315</v>
       </c>
       <c r="W50" s="3">
-        <v>4961.4333329658739</v>
+        <v>5992</v>
       </c>
       <c r="X50" s="5">
         <f t="shared" si="9"/>
-        <v>2171</v>
+        <v>5315</v>
       </c>
     </row>
     <row r="51" spans="11:24" x14ac:dyDescent="0.25">
@@ -8796,18 +8990,18 @@
       </c>
       <c r="L51" s="12">
         <f t="shared" si="4"/>
-        <v>664.9471092154281</v>
+        <v>4820.8917084304958</v>
       </c>
       <c r="N51" s="1">
-        <v>4975.1732492735446</v>
+        <v>6261.319435865018</v>
       </c>
       <c r="P51" s="1">
         <f t="shared" si="5"/>
-        <v>2.1556190120209067</v>
+        <v>137</v>
       </c>
       <c r="Q51" s="1">
         <f t="shared" si="6"/>
-        <v>4.6466933249859901</v>
+        <v>18769</v>
       </c>
       <c r="R51" s="8"/>
       <c r="T51" s="1">
@@ -8815,39 +9009,39 @@
       </c>
       <c r="U51" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V51" s="5">
         <f t="shared" si="8"/>
-        <v>533</v>
+        <v>4986</v>
       </c>
       <c r="W51" s="3">
-        <v>4960.5666670341261</v>
+        <v>5960</v>
       </c>
       <c r="X51" s="5">
         <f t="shared" si="9"/>
-        <v>533</v>
+        <v>4986</v>
       </c>
     </row>
     <row r="52" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K52" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="12">
         <f t="shared" si="4"/>
-        <v>4975.1732492735446</v>
+        <v>192.89170843049624</v>
       </c>
       <c r="N52" s="1">
-        <v>4973.0176302615237</v>
+        <v>6124.319435865018</v>
       </c>
       <c r="P52" s="1">
         <f t="shared" si="5"/>
-        <v>102.90456023246588</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="1">
         <f t="shared" si="6"/>
-        <v>10589.348516637199</v>
+        <v>31684</v>
       </c>
       <c r="R52" s="8"/>
       <c r="T52" s="1">
@@ -8859,35 +9053,35 @@
       </c>
       <c r="V52" s="5">
         <f t="shared" si="8"/>
-        <v>4853</v>
+        <v>358</v>
       </c>
       <c r="W52" s="3">
-        <v>4867.433332965873</v>
+        <v>5823</v>
       </c>
       <c r="X52" s="5">
         <f t="shared" si="9"/>
-        <v>4853</v>
+        <v>358</v>
       </c>
     </row>
     <row r="53" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K53" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="12">
         <f t="shared" si="4"/>
-        <v>906.39938933166104</v>
+        <v>5084.8917084304958</v>
       </c>
       <c r="N53" s="1">
-        <v>4870.1130700290578</v>
+        <v>5946.319435865018</v>
       </c>
       <c r="P53" s="1">
         <f t="shared" si="5"/>
-        <v>52.773859941883529</v>
+        <v>23</v>
       </c>
       <c r="Q53" s="1">
         <f t="shared" si="6"/>
-        <v>2785.0802931655389</v>
+        <v>529</v>
       </c>
       <c r="R53" s="8"/>
       <c r="T53" s="1">
@@ -8895,18 +9089,18 @@
       </c>
       <c r="U53" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V53" s="5">
         <f t="shared" si="8"/>
-        <v>794</v>
+        <v>5250</v>
       </c>
       <c r="W53" s="3">
-        <v>4849.5666670341261</v>
+        <v>5645</v>
       </c>
       <c r="X53" s="5">
         <f t="shared" si="9"/>
-        <v>794</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="54" spans="11:24" x14ac:dyDescent="0.25">
@@ -8916,18 +9110,18 @@
       </c>
       <c r="L54" s="12">
         <f t="shared" si="4"/>
-        <v>537.6255293897766</v>
+        <v>313.89170843049624</v>
       </c>
       <c r="N54" s="1">
-        <v>4817.3392100871743</v>
+        <v>5923.319435865018</v>
       </c>
       <c r="P54" s="1">
         <f t="shared" si="5"/>
-        <v>234.86929970941765</v>
+        <v>71</v>
       </c>
       <c r="Q54" s="1">
         <f t="shared" si="6"/>
-        <v>55163.587945992251</v>
+        <v>5041</v>
       </c>
       <c r="R54" s="8"/>
       <c r="T54" s="1">
@@ -8935,18 +9129,18 @@
       </c>
       <c r="U54" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V54" s="5">
         <f t="shared" si="8"/>
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="W54" s="3">
-        <v>4832.433332965873</v>
+        <v>5622</v>
       </c>
       <c r="X54" s="5">
         <f t="shared" si="9"/>
-        <v>435</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" spans="11:24" x14ac:dyDescent="0.25">
@@ -8956,18 +9150,18 @@
       </c>
       <c r="L55" s="12">
         <f t="shared" si="4"/>
-        <v>734.85166944789398</v>
+        <v>201.89170843049624</v>
       </c>
       <c r="N55" s="1">
-        <v>4582.4699103777566</v>
+        <v>5852.319435865018</v>
       </c>
       <c r="P55" s="1">
         <f t="shared" si="5"/>
-        <v>15.165960813629681</v>
+        <v>14</v>
       </c>
       <c r="Q55" s="1">
         <f t="shared" si="6"/>
-        <v>230.00636740055106</v>
+        <v>196</v>
       </c>
       <c r="R55" s="8"/>
       <c r="T55" s="1">
@@ -8979,14 +9173,14 @@
       </c>
       <c r="V55" s="5">
         <f t="shared" si="8"/>
-        <v>642</v>
+        <v>367</v>
       </c>
       <c r="W55" s="3">
-        <v>4756.433332965873</v>
+        <v>5551</v>
       </c>
       <c r="X55" s="5">
         <f t="shared" si="9"/>
-        <v>642</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="11:24" x14ac:dyDescent="0.25">
@@ -8996,18 +9190,18 @@
       </c>
       <c r="L56" s="12">
         <f t="shared" si="4"/>
-        <v>5132.0778095060095</v>
+        <v>5157.8917084304958</v>
       </c>
       <c r="N56" s="1">
-        <v>4567.3039495641269</v>
+        <v>5838.319435865018</v>
       </c>
       <c r="P56" s="1">
         <f t="shared" si="5"/>
-        <v>87.477198837672404</v>
+        <v>33</v>
       </c>
       <c r="Q56" s="1">
         <f t="shared" si="6"/>
-        <v>7652.2603164856746</v>
+        <v>1089</v>
       </c>
       <c r="R56" s="8"/>
       <c r="T56" s="1">
@@ -9019,14 +9213,14 @@
       </c>
       <c r="V56" s="5">
         <f t="shared" si="8"/>
-        <v>5049</v>
+        <v>5323</v>
       </c>
       <c r="W56" s="3">
-        <v>4733.566667034127</v>
+        <v>5537</v>
       </c>
       <c r="X56" s="5">
         <f t="shared" si="9"/>
-        <v>5049</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="57" spans="11:24" x14ac:dyDescent="0.25">
@@ -9036,18 +9230,18 @@
       </c>
       <c r="L57" s="12">
         <f t="shared" si="4"/>
-        <v>4567.3039495641269</v>
+        <v>5646.8917084304967</v>
       </c>
       <c r="N57" s="1">
-        <v>4479.8267507264545</v>
+        <v>5805.319435865018</v>
       </c>
       <c r="P57" s="1">
         <f t="shared" si="5"/>
-        <v>5.6182409298617131</v>
+        <v>194</v>
       </c>
       <c r="Q57" s="1">
         <f t="shared" si="6"/>
-        <v>31.564631145973408</v>
+        <v>37636</v>
       </c>
       <c r="R57" s="8"/>
       <c r="T57" s="1">
@@ -9059,35 +9253,35 @@
       </c>
       <c r="V57" s="5">
         <f t="shared" si="8"/>
-        <v>4494</v>
+        <v>5812</v>
       </c>
       <c r="W57" s="3">
-        <v>4669.433332965873</v>
+        <v>5504</v>
       </c>
       <c r="X57" s="5">
         <f t="shared" si="9"/>
-        <v>4494</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="58" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K58" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="12">
         <f t="shared" si="4"/>
-        <v>4013.5300896222425</v>
+        <v>116.89170843049624</v>
       </c>
       <c r="N58" s="1">
-        <v>4474.2085097965928</v>
+        <v>5611.319435865018</v>
       </c>
       <c r="P58" s="1">
         <f t="shared" si="5"/>
-        <v>352.15561901202182</v>
+        <v>241</v>
       </c>
       <c r="Q58" s="1">
         <f t="shared" si="6"/>
-        <v>124013.58000174027</v>
+        <v>58081</v>
       </c>
       <c r="R58" s="8"/>
       <c r="T58" s="1">
@@ -9099,14 +9293,14 @@
       </c>
       <c r="V58" s="5">
         <f t="shared" si="8"/>
-        <v>3950</v>
+        <v>282</v>
       </c>
       <c r="W58" s="3">
-        <v>4651.4333329658739</v>
+        <v>5310</v>
       </c>
       <c r="X58" s="5">
         <f t="shared" si="9"/>
-        <v>3950</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="11:24" x14ac:dyDescent="0.25">
@@ -9116,18 +9310,18 @@
       </c>
       <c r="L59" s="12">
         <f t="shared" si="4"/>
-        <v>1272.7562296803599</v>
+        <v>637.89170843049624</v>
       </c>
       <c r="N59" s="1">
-        <v>4122.052890784571</v>
+        <v>5370.319435865018</v>
       </c>
       <c r="P59" s="1">
         <f t="shared" si="5"/>
-        <v>108.52280116232851</v>
+        <v>280</v>
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="6"/>
-        <v>11777.19837211829</v>
+        <v>78400</v>
       </c>
       <c r="R59" s="8"/>
       <c r="T59" s="1">
@@ -9135,18 +9329,18 @@
       </c>
       <c r="U59" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V59" s="5">
         <f t="shared" si="8"/>
-        <v>1219</v>
+        <v>803</v>
       </c>
       <c r="W59" s="3">
-        <v>4645.5666670341261</v>
+        <v>5069</v>
       </c>
       <c r="X59" s="5">
         <f t="shared" si="9"/>
-        <v>1219</v>
+        <v>803</v>
       </c>
     </row>
     <row r="60" spans="11:24" x14ac:dyDescent="0.25">
@@ -9156,18 +9350,18 @@
       </c>
       <c r="L60" s="12">
         <f t="shared" si="4"/>
-        <v>5103.9823697384754</v>
+        <v>5150.8917084304958</v>
       </c>
       <c r="N60" s="1">
-        <v>4013.5300896222425</v>
+        <v>5090.319435865018</v>
       </c>
       <c r="P60" s="1">
         <f t="shared" si="5"/>
-        <v>322.09543976753412</v>
+        <v>75</v>
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="6"/>
-        <v>103745.4723190412</v>
+        <v>5625</v>
       </c>
       <c r="R60" s="8"/>
       <c r="T60" s="1">
@@ -9175,39 +9369,39 @@
       </c>
       <c r="U60" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V60" s="5">
         <f t="shared" si="8"/>
-        <v>5060</v>
+        <v>5316</v>
       </c>
       <c r="W60" s="3">
-        <v>4640.5666670341261</v>
+        <v>4789</v>
       </c>
       <c r="X60" s="5">
         <f t="shared" si="9"/>
-        <v>5060</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="61" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K61" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="12">
         <f t="shared" si="4"/>
-        <v>4474.2085097965928</v>
+        <v>-75.108291569503763</v>
       </c>
       <c r="N61" s="1">
-        <v>3691.4346498547084</v>
+        <v>5015.319435865018</v>
       </c>
       <c r="P61" s="1">
         <f t="shared" si="5"/>
-        <v>15.869299709417646</v>
+        <v>3570</v>
       </c>
       <c r="Q61" s="1">
         <f t="shared" si="6"/>
-        <v>251.83467326732298</v>
+        <v>12744900</v>
       </c>
       <c r="R61" s="8"/>
       <c r="T61" s="1">
@@ -9215,18 +9409,18 @@
       </c>
       <c r="U61" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V61" s="5">
         <f t="shared" si="8"/>
-        <v>4440</v>
+        <v>90</v>
       </c>
       <c r="W61" s="3">
-        <v>4635.4333329658739</v>
+        <v>4714</v>
       </c>
       <c r="X61" s="5">
         <f t="shared" si="9"/>
-        <v>4440</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="11:24" x14ac:dyDescent="0.25">
@@ -9236,18 +9430,18 @@
       </c>
       <c r="L62" s="12">
         <f t="shared" si="4"/>
-        <v>3691.4346498547084</v>
+        <v>5707.8917084304958</v>
       </c>
       <c r="N62" s="1">
-        <v>3675.5653501452907</v>
+        <v>1445.319435865018</v>
       </c>
       <c r="P62" s="1">
         <f t="shared" si="5"/>
-        <v>229.74894122044407</v>
+        <v>366</v>
       </c>
       <c r="Q62" s="1">
         <f t="shared" si="6"/>
-        <v>52784.575991915066</v>
+        <v>133956</v>
       </c>
       <c r="R62" s="8"/>
       <c r="T62" s="1">
@@ -9259,14 +9453,14 @@
       </c>
       <c r="V62" s="5">
         <f t="shared" si="8"/>
-        <v>3667</v>
+        <v>5873</v>
       </c>
       <c r="W62" s="3">
-        <v>4570.433332965873</v>
+        <v>1144</v>
       </c>
       <c r="X62" s="5">
         <f t="shared" si="9"/>
-        <v>3667</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="63" spans="11:24" x14ac:dyDescent="0.25">
@@ -9276,18 +9470,18 @@
       </c>
       <c r="L63" s="12">
         <f t="shared" si="4"/>
-        <v>765.66078991282484</v>
+        <v>179.89170843049624</v>
       </c>
       <c r="N63" s="1">
-        <v>3445.8164089248467</v>
+        <v>1079.319435865018</v>
       </c>
       <c r="P63" s="1">
         <f t="shared" si="5"/>
-        <v>514.3215798256515</v>
+        <v>155</v>
       </c>
       <c r="Q63" s="1">
         <f t="shared" si="6"/>
-        <v>264526.687474354</v>
+        <v>24025</v>
       </c>
       <c r="R63" s="8"/>
       <c r="T63" s="1">
@@ -9299,35 +9493,35 @@
       </c>
       <c r="V63" s="5">
         <f t="shared" si="8"/>
-        <v>751</v>
+        <v>345</v>
       </c>
       <c r="W63" s="3">
-        <v>4523.566667034127</v>
+        <v>778</v>
       </c>
       <c r="X63" s="5">
         <f t="shared" si="9"/>
-        <v>751</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K64" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12">
         <f t="shared" si="4"/>
-        <v>363.88692997094131</v>
+        <v>5208.8917084304958</v>
       </c>
       <c r="N64" s="1">
-        <v>2931.4948290991952</v>
+        <v>924.31943586501802</v>
       </c>
       <c r="P64" s="1">
         <f t="shared" si="5"/>
-        <v>618.77385994188262</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="1">
         <f t="shared" si="6"/>
-        <v>382881.08974737657</v>
+        <v>0</v>
       </c>
       <c r="R64" s="8"/>
       <c r="T64" s="1">
@@ -9335,18 +9529,18 @@
       </c>
       <c r="U64" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V64" s="5">
         <f t="shared" si="8"/>
-        <v>359</v>
+        <v>5374</v>
       </c>
       <c r="W64" s="3">
-        <v>1358.5666670341261</v>
+        <v>623</v>
       </c>
       <c r="X64" s="5">
         <f t="shared" si="9"/>
-        <v>359</v>
+        <v>5374</v>
       </c>
     </row>
     <row r="65" spans="11:24" x14ac:dyDescent="0.25">
@@ -9356,18 +9550,18 @@
       </c>
       <c r="L65" s="12">
         <f t="shared" si="4"/>
-        <v>4870.1130700290578</v>
+        <v>6320.8917084304967</v>
       </c>
       <c r="N65" s="1">
-        <v>2312.7209691573125</v>
+        <v>924.31943586501802</v>
       </c>
       <c r="P65" s="1">
         <f t="shared" si="5"/>
-        <v>757.92947895390535</v>
+        <v>79</v>
       </c>
       <c r="Q65" s="1">
         <f t="shared" si="6"/>
-        <v>574457.09506733844</v>
+        <v>6241</v>
       </c>
       <c r="R65" s="8"/>
       <c r="T65" s="1">
@@ -9375,18 +9569,18 @@
       </c>
       <c r="U65" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V65" s="5">
         <f t="shared" si="8"/>
-        <v>4875</v>
+        <v>6486</v>
       </c>
       <c r="W65" s="3">
-        <v>976.56666703412702</v>
+        <v>623</v>
       </c>
       <c r="X65" s="5">
         <f t="shared" si="9"/>
-        <v>4875</v>
+        <v>6486</v>
       </c>
     </row>
     <row r="66" spans="11:24" x14ac:dyDescent="0.25">
@@ -9396,18 +9590,18 @@
       </c>
       <c r="L66" s="12">
         <f t="shared" si="4"/>
-        <v>4817.3392100871743</v>
+        <v>6219.8917084304958</v>
       </c>
       <c r="N66" s="1">
-        <v>1554.7914902034072</v>
+        <v>845.31943586501802</v>
       </c>
       <c r="P66" s="1">
         <f t="shared" si="5"/>
-        <v>240.74894122044498</v>
+        <v>54</v>
       </c>
       <c r="Q66" s="1">
         <f t="shared" si="6"/>
-        <v>57960.05269876527</v>
+        <v>2916</v>
       </c>
       <c r="R66" s="8"/>
       <c r="T66" s="1">
@@ -9415,18 +9609,18 @@
       </c>
       <c r="U66" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V66" s="5">
         <f t="shared" si="8"/>
-        <v>4832</v>
+        <v>6385</v>
       </c>
       <c r="W66" s="3">
-        <v>676.43333296587389</v>
+        <v>544</v>
       </c>
       <c r="X66" s="5">
         <f t="shared" si="9"/>
-        <v>4832</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="67" spans="11:24" x14ac:dyDescent="0.25">
@@ -9436,18 +9630,18 @@
       </c>
       <c r="L67" s="12">
         <f t="shared" si="4"/>
-        <v>3675.5653501452907</v>
+        <v>6415.8917084304958</v>
       </c>
       <c r="N67" s="1">
-        <v>1314.0425489829622</v>
+        <v>791.31943586501802</v>
       </c>
       <c r="P67" s="1">
         <f t="shared" si="5"/>
-        <v>41.286319302602351</v>
+        <v>101</v>
       </c>
       <c r="Q67" s="1">
         <f t="shared" si="6"/>
-        <v>1704.5601615564356</v>
+        <v>10201</v>
       </c>
       <c r="R67" s="8"/>
       <c r="T67" s="1">
@@ -9455,39 +9649,39 @@
       </c>
       <c r="U67" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V67" s="5">
         <f t="shared" si="8"/>
-        <v>3700</v>
+        <v>6581</v>
       </c>
       <c r="W67" s="3">
-        <v>518.56666703412702</v>
+        <v>490</v>
       </c>
       <c r="X67" s="5">
         <f t="shared" si="9"/>
-        <v>3700</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="68" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K68" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="12">
         <f t="shared" si="4"/>
-        <v>1554.7914902034072</v>
+        <v>6128.8917084304958</v>
       </c>
       <c r="N68" s="1">
-        <v>1272.7562296803599</v>
+        <v>690.31943586501802</v>
       </c>
       <c r="P68" s="1">
         <f t="shared" si="5"/>
-        <v>195.4771988376724</v>
+        <v>28</v>
       </c>
       <c r="Q68" s="1">
         <f t="shared" si="6"/>
-        <v>38211.335265422917</v>
+        <v>784</v>
       </c>
       <c r="R68" s="8"/>
       <c r="T68" s="1">
@@ -9499,14 +9693,14 @@
       </c>
       <c r="V68" s="5">
         <f t="shared" si="8"/>
-        <v>1589</v>
+        <v>6294</v>
       </c>
       <c r="W68" s="3">
-        <v>495.43333296587389</v>
+        <v>389</v>
       </c>
       <c r="X68" s="5">
         <f t="shared" si="9"/>
-        <v>1589</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="69" spans="11:24" x14ac:dyDescent="0.25">
@@ -9516,18 +9710,18 @@
       </c>
       <c r="L69" s="12">
         <f t="shared" si="4"/>
-        <v>4973.0176302615237</v>
+        <v>5681.8917084304958</v>
       </c>
       <c r="N69" s="1">
-        <v>1077.2790308426875</v>
+        <v>662.31943586501802</v>
       </c>
       <c r="P69" s="1">
         <f t="shared" si="5"/>
-        <v>170.87964151102642</v>
+        <v>28</v>
       </c>
       <c r="Q69" s="1">
         <f t="shared" si="6"/>
-        <v>29199.851882936902</v>
+        <v>784</v>
       </c>
       <c r="R69" s="8"/>
       <c r="T69" s="1">
@@ -9539,14 +9733,14 @@
       </c>
       <c r="V69" s="5">
         <f t="shared" si="8"/>
-        <v>5017</v>
+        <v>5847</v>
       </c>
       <c r="W69" s="3">
-        <v>494.56666703412657</v>
+        <v>361</v>
       </c>
       <c r="X69" s="5">
         <f t="shared" si="9"/>
-        <v>5017</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="70" spans="11:24" x14ac:dyDescent="0.25">
@@ -9556,18 +9750,18 @@
       </c>
       <c r="L70" s="12">
         <f t="shared" si="4"/>
-        <v>892.24377031964013</v>
+        <v>98.891708430496237</v>
       </c>
       <c r="N70" s="1">
-        <v>906.39938933166104</v>
+        <v>634.31943586501802</v>
       </c>
       <c r="P70" s="1">
         <f t="shared" si="5"/>
-        <v>14.155619012020907</v>
+        <v>42</v>
       </c>
       <c r="Q70" s="1">
         <f t="shared" si="6"/>
-        <v>200.38154961348775</v>
+        <v>1764</v>
       </c>
       <c r="R70" s="8"/>
       <c r="T70" s="1">
@@ -9579,35 +9773,35 @@
       </c>
       <c r="V70" s="5">
         <f t="shared" si="8"/>
-        <v>946</v>
+        <v>264</v>
       </c>
       <c r="W70" s="3">
-        <v>454.56666703412611</v>
+        <v>333</v>
       </c>
       <c r="X70" s="5">
         <f t="shared" si="9"/>
-        <v>946</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K71" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="12">
         <f t="shared" si="4"/>
-        <v>4582.4699103777566</v>
+        <v>823.89170843049624</v>
       </c>
       <c r="N71" s="1">
-        <v>892.24377031964013</v>
+        <v>592.31943586501802</v>
       </c>
       <c r="P71" s="1">
         <f t="shared" si="5"/>
-        <v>72.06017924448679</v>
+        <v>31</v>
       </c>
       <c r="Q71" s="1">
         <f t="shared" si="6"/>
-        <v>5192.6694327475643</v>
+        <v>961</v>
       </c>
       <c r="R71" s="8"/>
       <c r="T71" s="1">
@@ -9615,39 +9809,39 @@
       </c>
       <c r="U71" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V71" s="5">
         <f t="shared" si="8"/>
-        <v>4646</v>
+        <v>989</v>
       </c>
       <c r="W71" s="3">
-        <v>448.43333296587389</v>
+        <v>291</v>
       </c>
       <c r="X71" s="5">
         <f t="shared" si="9"/>
-        <v>4646</v>
+        <v>989</v>
       </c>
     </row>
     <row r="72" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K72" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="12">
         <f t="shared" si="4"/>
-        <v>807.69605043587308</v>
+        <v>5559.8917084304958</v>
       </c>
       <c r="N72" s="1">
-        <v>820.18359107515334</v>
+        <v>561.31943586501802</v>
       </c>
       <c r="P72" s="1">
         <f t="shared" si="5"/>
-        <v>12.487540639280269</v>
+        <v>21</v>
       </c>
       <c r="Q72" s="1">
         <f t="shared" si="6"/>
-        <v>155.93867121767627</v>
+        <v>441</v>
       </c>
       <c r="R72" s="8"/>
       <c r="T72" s="1">
@@ -9659,35 +9853,35 @@
       </c>
       <c r="V72" s="5">
         <f t="shared" si="8"/>
-        <v>881</v>
+        <v>5725</v>
       </c>
       <c r="W72" s="3">
-        <v>384.56666703412611</v>
+        <v>260</v>
       </c>
       <c r="X72" s="5">
         <f t="shared" si="9"/>
-        <v>881</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="73" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K73" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12">
         <f t="shared" si="4"/>
-        <v>5258.9221904939886</v>
+        <v>128.89170843049624</v>
       </c>
       <c r="N73" s="1">
-        <v>807.69605043587308</v>
+        <v>540.31943586501802</v>
       </c>
       <c r="P73" s="1">
         <f t="shared" si="5"/>
-        <v>42.035260523048237</v>
+        <v>14</v>
       </c>
       <c r="Q73" s="1">
         <f t="shared" si="6"/>
-        <v>1766.9631272405375</v>
+        <v>196</v>
       </c>
       <c r="R73" s="8"/>
       <c r="T73" s="1">
@@ -9699,14 +9893,14 @@
       </c>
       <c r="V73" s="5">
         <f t="shared" si="8"/>
-        <v>5342</v>
+        <v>294</v>
       </c>
       <c r="W73" s="3">
-        <v>338.43333296587389</v>
+        <v>239</v>
       </c>
       <c r="X73" s="5">
         <f t="shared" si="9"/>
-        <v>5342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="11:24" x14ac:dyDescent="0.25">
@@ -9716,18 +9910,18 @@
       </c>
       <c r="L74" s="12">
         <f t="shared" si="4"/>
-        <v>158.14833055210511</v>
+        <v>169.89170843049624</v>
       </c>
       <c r="N74" s="1">
-        <v>765.66078991282484</v>
+        <v>526.31943586501802</v>
       </c>
       <c r="P74" s="1">
         <f t="shared" si="5"/>
-        <v>30.809120464930857</v>
+        <v>10</v>
       </c>
       <c r="Q74" s="1">
         <f t="shared" si="6"/>
-        <v>949.20190382262126</v>
+        <v>100</v>
       </c>
       <c r="R74" s="8"/>
       <c r="T74" s="1">
@@ -9735,39 +9929,39 @@
       </c>
       <c r="U74" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V74" s="5">
         <f t="shared" si="8"/>
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="W74" s="3">
-        <v>308.56666703412702</v>
+        <v>225</v>
       </c>
       <c r="X74" s="5">
         <f t="shared" si="9"/>
-        <v>251</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K75" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="12">
         <f t="shared" si="4"/>
-        <v>473.37447061022158</v>
+        <v>6075.8917084304958</v>
       </c>
       <c r="N75" s="1">
-        <v>734.85166944789398</v>
+        <v>516.31943586501802</v>
       </c>
       <c r="P75" s="1">
         <f t="shared" si="5"/>
-        <v>69.904560232465883</v>
+        <v>16</v>
       </c>
       <c r="Q75" s="1">
         <f t="shared" si="6"/>
-        <v>4886.647541294451</v>
+        <v>256</v>
       </c>
       <c r="R75" s="8"/>
       <c r="T75" s="1">
@@ -9779,14 +9973,14 @@
       </c>
       <c r="V75" s="5">
         <f t="shared" si="8"/>
-        <v>576</v>
+        <v>6241</v>
       </c>
       <c r="W75" s="3">
-        <v>297.43333296587389</v>
+        <v>215</v>
       </c>
       <c r="X75" s="5">
         <f t="shared" si="9"/>
-        <v>576</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="76" spans="11:24" x14ac:dyDescent="0.25">
@@ -9796,18 +9990,18 @@
       </c>
       <c r="L76" s="12">
         <f t="shared" si="4"/>
-        <v>5044.600610668338</v>
+        <v>5649.8917084304967</v>
       </c>
       <c r="N76" s="1">
-        <v>664.9471092154281</v>
+        <v>500.31943586501802</v>
       </c>
       <c r="P76" s="1">
         <f t="shared" si="5"/>
-        <v>127.3215798256515</v>
+        <v>9</v>
       </c>
       <c r="Q76" s="1">
         <f t="shared" si="6"/>
-        <v>16210.784689299746</v>
+        <v>81</v>
       </c>
       <c r="R76" s="8"/>
       <c r="T76" s="1">
@@ -9819,35 +10013,35 @@
       </c>
       <c r="V76" s="5">
         <f t="shared" si="8"/>
-        <v>5157</v>
+        <v>5815</v>
       </c>
       <c r="W76" s="3">
-        <v>256.56666703412702</v>
+        <v>199</v>
       </c>
       <c r="X76" s="5">
         <f t="shared" si="9"/>
-        <v>5157</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="77" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K77" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12">
         <f t="shared" si="4"/>
-        <v>4479.8267507264545</v>
+        <v>152.89170843049624</v>
       </c>
       <c r="N77" s="1">
-        <v>537.6255293897766</v>
+        <v>491.31943586501802</v>
       </c>
       <c r="P77" s="1">
         <f t="shared" si="5"/>
-        <v>13.894218430856199</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="1">
         <f t="shared" si="6"/>
-        <v>193.0493058043441</v>
+        <v>9</v>
       </c>
       <c r="R77" s="8"/>
       <c r="T77" s="1">
@@ -9859,14 +10053,14 @@
       </c>
       <c r="V77" s="5">
         <f t="shared" si="8"/>
-        <v>4602</v>
+        <v>318</v>
       </c>
       <c r="W77" s="3">
-        <v>192.56666703412702</v>
+        <v>190</v>
       </c>
       <c r="X77" s="5">
         <f t="shared" si="9"/>
-        <v>4602</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" spans="11:24" x14ac:dyDescent="0.25">
@@ -9876,18 +10070,18 @@
       </c>
       <c r="L78" s="12">
         <f t="shared" si="4"/>
-        <v>4122.052890784571</v>
+        <v>5536.8917084304958</v>
       </c>
       <c r="N78" s="1">
-        <v>523.7313109589204</v>
+        <v>488.31943586501802</v>
       </c>
       <c r="P78" s="1">
         <f t="shared" si="5"/>
-        <v>35.462621917840806</v>
+        <v>16</v>
       </c>
       <c r="Q78" s="1">
         <f t="shared" si="6"/>
-        <v>1257.5975532877233</v>
+        <v>256</v>
       </c>
       <c r="R78" s="8"/>
       <c r="T78" s="1">
@@ -9895,18 +10089,18 @@
       </c>
       <c r="U78" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V78" s="5">
         <f t="shared" si="8"/>
-        <v>4254</v>
+        <v>5702</v>
       </c>
       <c r="W78" s="3">
-        <v>186.43333296587389</v>
+        <v>187</v>
       </c>
       <c r="X78" s="5">
         <f t="shared" si="9"/>
-        <v>4254</v>
+        <v>5702</v>
       </c>
     </row>
     <row r="79" spans="11:24" x14ac:dyDescent="0.25">
@@ -9916,18 +10110,18 @@
       </c>
       <c r="L79" s="12">
         <f t="shared" si="4"/>
-        <v>1077.2790308426875</v>
+        <v>-132.10829156950376</v>
       </c>
       <c r="N79" s="1">
-        <v>488.2686890410796</v>
+        <v>472.31943586501802</v>
       </c>
       <c r="P79" s="1">
         <f t="shared" si="5"/>
-        <v>14.894218430858018</v>
+        <v>21</v>
       </c>
       <c r="Q79" s="1">
         <f t="shared" si="6"/>
-        <v>221.83774266611067</v>
+        <v>441</v>
       </c>
       <c r="R79" s="8"/>
       <c r="T79" s="1">
@@ -9935,39 +10129,39 @@
       </c>
       <c r="U79" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V79" s="5">
         <f t="shared" si="8"/>
-        <v>1219</v>
+        <v>33</v>
       </c>
       <c r="W79" s="3">
-        <v>139.43333296587389</v>
+        <v>171</v>
       </c>
       <c r="X79" s="5">
         <f t="shared" si="9"/>
-        <v>1219</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="11:24" x14ac:dyDescent="0.25">
       <c r="K80" s="1">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="12">
         <f t="shared" si="4"/>
-        <v>5104.5051709008039</v>
+        <v>133.89170843049624</v>
       </c>
       <c r="N80" s="1">
-        <v>473.37447061022158</v>
+        <v>451.31943586501802</v>
       </c>
       <c r="P80" s="1">
         <f t="shared" si="5"/>
-        <v>109.48754063928027</v>
+        <v>7</v>
       </c>
       <c r="Q80" s="1">
         <f t="shared" si="6"/>
-        <v>11987.521555238049</v>
+        <v>49</v>
       </c>
       <c r="R80" s="8"/>
       <c r="T80" s="1">
@@ -9979,35 +10173,35 @@
       </c>
       <c r="V80" s="5">
         <f t="shared" si="8"/>
-        <v>5256</v>
+        <v>299</v>
       </c>
       <c r="W80" s="3">
-        <v>99.433332965873433</v>
+        <v>150</v>
       </c>
       <c r="X80" s="5">
         <f t="shared" si="9"/>
-        <v>5256</v>
+        <v>299</v>
       </c>
     </row>
     <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="K81" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="12">
         <f t="shared" si="4"/>
-        <v>523.7313109589204</v>
+        <v>5861.8917084304958</v>
       </c>
       <c r="N81" s="1">
-        <v>363.88692997094131</v>
+        <v>444.31943586501802</v>
       </c>
       <c r="P81" s="1">
         <f t="shared" si="5"/>
-        <v>205.7385994188362</v>
+        <v>16</v>
       </c>
       <c r="Q81" s="1">
         <f t="shared" si="6"/>
-        <v>42328.371290824347</v>
+        <v>256</v>
       </c>
       <c r="R81" s="8"/>
       <c r="T81" s="1">
@@ -10015,39 +10209,39 @@
       </c>
       <c r="U81" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>+</v>
+        <v>-</v>
       </c>
       <c r="V81" s="5">
         <f t="shared" si="8"/>
-        <v>685</v>
+        <v>6027</v>
       </c>
       <c r="W81" s="3">
-        <v>63.566667034126112</v>
+        <v>143</v>
       </c>
       <c r="X81" s="5">
         <f t="shared" si="9"/>
-        <v>685</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="K82" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="12">
         <f t="shared" si="4"/>
-        <v>-52.042548982963126</v>
+        <v>6361.8917084304958</v>
       </c>
       <c r="N82" s="1">
-        <v>158.14833055210511</v>
+        <v>428.31943586501802</v>
       </c>
       <c r="P82" s="1">
         <f t="shared" si="5"/>
-        <v>210.19087953506823</v>
+        <v>56</v>
       </c>
       <c r="Q82" s="1">
         <f t="shared" si="6"/>
-        <v>44180.205839725568</v>
+        <v>3136</v>
       </c>
       <c r="R82" s="8"/>
       <c r="T82" s="1">
@@ -10055,18 +10249,18 @@
       </c>
       <c r="U82" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>-</v>
+        <v>+</v>
       </c>
       <c r="V82" s="5">
         <f t="shared" si="8"/>
-        <v>119</v>
+        <v>6527</v>
       </c>
       <c r="W82" s="3">
-        <v>17.566667034127022</v>
+        <v>127</v>
       </c>
       <c r="X82" s="5">
         <f t="shared" si="9"/>
-        <v>119</v>
+        <v>6527</v>
       </c>
     </row>
     <row r="83" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10076,10 +10270,10 @@
       </c>
       <c r="L83" s="12">
         <f t="shared" si="4"/>
-        <v>820.18359107515334</v>
+        <v>1124.8917084304962</v>
       </c>
       <c r="N83" s="1">
-        <v>-52.042548982963126</v>
+        <v>372.31943586501802</v>
       </c>
       <c r="R83" s="9"/>
       <c r="T83" s="1">
@@ -10091,14 +10285,14 @@
       </c>
       <c r="V83" s="5">
         <f t="shared" si="8"/>
-        <v>1001</v>
+        <v>1290</v>
       </c>
       <c r="W83" s="4">
-        <v>17.566667034126112</v>
+        <v>71</v>
       </c>
       <c r="X83" s="5">
         <f t="shared" si="9"/>
-        <v>1001</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="85" spans="1:49" x14ac:dyDescent="0.25">
@@ -10109,7 +10303,7 @@
     <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="N86" s="1">
         <f>INDEX(N46:N83,MATCH(R46,P46:P82,0))</f>
-        <v>2312.7209691573125</v>
+        <v>5015.319435865018</v>
       </c>
     </row>
     <row r="90" spans="1:49" x14ac:dyDescent="0.25">
@@ -10257,22 +10451,22 @@
     <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <f t="shared" ref="A94:A131" si="10">$J$100*D94+$J$99</f>
-        <v>2483</v>
+        <v>3233.2834008097166</v>
       </c>
       <c r="B94" s="1">
         <f>(A94+C94)/2</f>
-        <v>2564.3286376428396</v>
+        <v>3309.4984857941954</v>
       </c>
       <c r="C94" s="1">
         <f>$J$97*D94+$J$96</f>
-        <v>2645.6572752856796</v>
+        <v>3385.7135707786747</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
       </c>
       <c r="E94" s="1">
         <f>V46</f>
-        <v>3265</v>
+        <v>5550</v>
       </c>
       <c r="F94" s="1">
         <f>D94^2</f>
@@ -10280,28 +10474,28 @@
       </c>
       <c r="G94" s="1">
         <f>E94*D94</f>
-        <v>3265</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <f t="shared" si="10"/>
-        <v>2492.2830725462304</v>
+        <v>3241.8655213918369</v>
       </c>
       <c r="B95" s="1">
         <f t="shared" ref="B95:B131" si="11">(A95+C95)/2</f>
-        <v>2569.2155676137818</v>
+        <v>3313.9608720528308</v>
       </c>
       <c r="C95" s="1">
         <f t="shared" ref="C95:C131" si="12">$J$97*D95+$J$96</f>
-        <v>2646.1480626813327</v>
+        <v>3386.0562227138248</v>
       </c>
       <c r="D95" s="1">
         <v>2</v>
       </c>
       <c r="E95" s="1">
         <f t="shared" ref="E95:E131" si="13">V47</f>
-        <v>1143</v>
+        <v>438</v>
       </c>
       <c r="F95" s="1">
         <f t="shared" ref="F95:F131" si="14">D95^2</f>
@@ -10309,28 +10503,28 @@
       </c>
       <c r="G95" s="1">
         <f t="shared" ref="G95:G131" si="15">E95*D95</f>
-        <v>2286</v>
+        <v>876</v>
       </c>
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <f t="shared" si="10"/>
-        <v>2501.5661450924608</v>
+        <v>3250.4476419739576</v>
       </c>
       <c r="B96" s="1">
         <f t="shared" si="11"/>
-        <v>2574.1024975847231</v>
+        <v>3318.4232583114663</v>
       </c>
       <c r="C96" s="1">
         <f t="shared" si="12"/>
-        <v>2646.6388500769858</v>
+        <v>3386.3988746489745</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96" s="1">
         <f t="shared" si="13"/>
-        <v>327</v>
+        <v>587</v>
       </c>
       <c r="F96" s="1">
         <f t="shared" si="14"/>
@@ -10338,35 +10532,35 @@
       </c>
       <c r="G96" s="1">
         <f t="shared" si="15"/>
-        <v>981</v>
+        <v>1761</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>14</v>
       </c>
       <c r="J96" s="1">
         <f>(SUM(E94:E131)*SUM(E94:E131)-SUM(D94:D131)*SUM(G94:G131))/(38*SUM(E94:E131)-SUM(D94:D131)^2)</f>
-        <v>2645.1664878900265</v>
+        <v>3385.370918843525</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <f t="shared" si="10"/>
-        <v>2510.8492176386912</v>
+        <v>3259.0297625560784</v>
       </c>
       <c r="B97" s="1">
         <f t="shared" si="11"/>
-        <v>2578.9894275556653</v>
+        <v>3322.8856445701012</v>
       </c>
       <c r="C97" s="1">
         <f t="shared" si="12"/>
-        <v>2647.1296374726389</v>
+        <v>3386.7415265841246</v>
       </c>
       <c r="D97" s="1">
         <v>4</v>
       </c>
       <c r="E97" s="1">
         <f t="shared" si="13"/>
-        <v>2780</v>
+        <v>4898</v>
       </c>
       <c r="F97" s="1">
         <f t="shared" si="14"/>
@@ -10374,35 +10568,35 @@
       </c>
       <c r="G97" s="1">
         <f t="shared" si="15"/>
-        <v>11120</v>
+        <v>19592</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>20</v>
       </c>
       <c r="J97" s="1">
         <f>(38*SUM(G94:G131)-SUM(E94:E131)*SUM(D94:D131))/(38*SUM(E94:E131)-SUM(D94:D131)^2)</f>
-        <v>0.49078739565315482</v>
+        <v>0.34265193514987091</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <f t="shared" si="10"/>
-        <v>2520.1322901849217</v>
+        <v>3267.6118831381987</v>
       </c>
       <c r="B98" s="1">
         <f t="shared" si="11"/>
-        <v>2583.8763575266066</v>
+        <v>3327.3480308287362</v>
       </c>
       <c r="C98" s="1">
         <f t="shared" si="12"/>
-        <v>2647.620424868292</v>
+        <v>3387.0841785192742</v>
       </c>
       <c r="D98" s="1">
         <v>5</v>
       </c>
       <c r="E98" s="1">
         <f t="shared" si="13"/>
-        <v>2171</v>
+        <v>5315</v>
       </c>
       <c r="F98" s="1">
         <f t="shared" si="14"/>
@@ -10410,29 +10604,29 @@
       </c>
       <c r="G98" s="1">
         <f t="shared" si="15"/>
-        <v>10855</v>
+        <v>26575</v>
       </c>
       <c r="I98" s="11"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <f t="shared" si="10"/>
-        <v>2529.4153627311521</v>
+        <v>3276.1940037203194</v>
       </c>
       <c r="B99" s="1">
         <f t="shared" si="11"/>
-        <v>2588.7632874975488</v>
+        <v>3331.8104170873721</v>
       </c>
       <c r="C99" s="1">
         <f t="shared" si="12"/>
-        <v>2648.1112122639456</v>
+        <v>3387.4268304544244</v>
       </c>
       <c r="D99" s="1">
         <v>6</v>
       </c>
       <c r="E99" s="1">
         <f t="shared" si="13"/>
-        <v>533</v>
+        <v>4986</v>
       </c>
       <c r="F99" s="1">
         <f t="shared" si="14"/>
@@ -10440,35 +10634,35 @@
       </c>
       <c r="G99" s="1">
         <f t="shared" si="15"/>
-        <v>3198</v>
+        <v>29916</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>21</v>
       </c>
       <c r="J99" s="1">
         <f>(SUM(E94:E131)*SUM(F94:F131)-SUM(D94:D131)*SUM(G94:G131))/(38*SUM(F94:F131)-SUM(D94:D131)^2)</f>
-        <v>2473.7169274537696</v>
+        <v>3224.7012802275958</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <f t="shared" si="10"/>
-        <v>2538.6984352773825</v>
+        <v>3284.7761243024397</v>
       </c>
       <c r="B100" s="1">
         <f t="shared" si="11"/>
-        <v>2593.6502174684906</v>
+        <v>3336.2728033460071</v>
       </c>
       <c r="C100" s="1">
         <f t="shared" si="12"/>
-        <v>2648.6019996595987</v>
+        <v>3387.769482389574</v>
       </c>
       <c r="D100" s="1">
         <v>7</v>
       </c>
       <c r="E100" s="1">
         <f t="shared" si="13"/>
-        <v>4853</v>
+        <v>358</v>
       </c>
       <c r="F100" s="1">
         <f t="shared" si="14"/>
@@ -10476,35 +10670,35 @@
       </c>
       <c r="G100" s="1">
         <f t="shared" si="15"/>
-        <v>33971</v>
+        <v>2506</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>15</v>
       </c>
       <c r="J100" s="1">
         <f>(38*SUM(G94:G131)-SUM(E94:E131)*SUM(D94:D131))/(38*SUM(F94:F131)-SUM(D94:D131)^2)</f>
-        <v>9.2830725462304411</v>
+        <v>8.5821205821205826</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <f t="shared" si="10"/>
-        <v>2547.9815078236129</v>
+        <v>3293.3582448845605</v>
       </c>
       <c r="B101" s="1">
         <f t="shared" si="11"/>
-        <v>2598.5371474394324</v>
+        <v>3340.7351896046421</v>
       </c>
       <c r="C101" s="1">
         <f t="shared" si="12"/>
-        <v>2649.0927870552518</v>
+        <v>3388.1121343247241</v>
       </c>
       <c r="D101" s="1">
         <v>8</v>
       </c>
       <c r="E101" s="1">
         <f t="shared" si="13"/>
-        <v>794</v>
+        <v>5250</v>
       </c>
       <c r="F101" s="1">
         <f t="shared" si="14"/>
@@ -10512,28 +10706,28 @@
       </c>
       <c r="G101" s="1">
         <f t="shared" si="15"/>
-        <v>6352</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <f t="shared" si="10"/>
-        <v>2557.2645803698438</v>
+        <v>3301.9403654666812</v>
       </c>
       <c r="B102" s="1">
         <f t="shared" si="11"/>
-        <v>2603.4240774103746</v>
+        <v>3345.1975758632775</v>
       </c>
       <c r="C102" s="1">
         <f t="shared" si="12"/>
-        <v>2649.583574450905</v>
+        <v>3388.4547862598738</v>
       </c>
       <c r="D102" s="1">
         <v>9</v>
       </c>
       <c r="E102" s="1">
         <f t="shared" si="13"/>
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="F102" s="1">
         <f t="shared" si="14"/>
@@ -10541,28 +10735,28 @@
       </c>
       <c r="G102" s="1">
         <f t="shared" si="15"/>
-        <v>3915</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <f t="shared" si="10"/>
-        <v>2566.5476529160742</v>
+        <v>3310.5224860488015</v>
       </c>
       <c r="B103" s="1">
         <f t="shared" si="11"/>
-        <v>2608.3110073813159</v>
+        <v>3349.6599621219129</v>
       </c>
       <c r="C103" s="1">
         <f t="shared" si="12"/>
-        <v>2650.0743618465581</v>
+        <v>3388.7974381950239</v>
       </c>
       <c r="D103" s="1">
         <v>10</v>
       </c>
       <c r="E103" s="1">
         <f t="shared" si="13"/>
-        <v>642</v>
+        <v>367</v>
       </c>
       <c r="F103" s="1">
         <f t="shared" si="14"/>
@@ -10570,28 +10764,28 @@
       </c>
       <c r="G103" s="1">
         <f t="shared" si="15"/>
-        <v>6420</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <f t="shared" si="10"/>
-        <v>2575.8307254623046</v>
+        <v>3319.1046066309223</v>
       </c>
       <c r="B104" s="1">
         <f t="shared" si="11"/>
-        <v>2613.1979373522581</v>
+        <v>3354.1223483805479</v>
       </c>
       <c r="C104" s="1">
         <f t="shared" si="12"/>
-        <v>2650.5651492422112</v>
+        <v>3389.1400901301736</v>
       </c>
       <c r="D104" s="1">
         <v>11</v>
       </c>
       <c r="E104" s="1">
         <f t="shared" si="13"/>
-        <v>5049</v>
+        <v>5323</v>
       </c>
       <c r="F104" s="1">
         <f t="shared" si="14"/>
@@ -10599,28 +10793,28 @@
       </c>
       <c r="G104" s="1">
         <f t="shared" si="15"/>
-        <v>55539</v>
+        <v>58553</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <f t="shared" si="10"/>
-        <v>2585.113798008535</v>
+        <v>3327.686727213043</v>
       </c>
       <c r="B105" s="1">
         <f t="shared" si="11"/>
-        <v>2618.0848673231994</v>
+        <v>3358.5847346391834</v>
       </c>
       <c r="C105" s="1">
         <f t="shared" si="12"/>
-        <v>2651.0559366378643</v>
+        <v>3389.4827420653237</v>
       </c>
       <c r="D105" s="1">
         <v>12</v>
       </c>
       <c r="E105" s="1">
         <f t="shared" si="13"/>
-        <v>4494</v>
+        <v>5812</v>
       </c>
       <c r="F105" s="1">
         <f t="shared" si="14"/>
@@ -10628,28 +10822,28 @@
       </c>
       <c r="G105" s="1">
         <f t="shared" si="15"/>
-        <v>53928</v>
+        <v>69744</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <f t="shared" si="10"/>
-        <v>2594.3968705547654</v>
+        <v>3336.2688477951633</v>
       </c>
       <c r="B106" s="1">
         <f t="shared" si="11"/>
-        <v>2622.9717972941417</v>
+        <v>3363.0471208978183</v>
       </c>
       <c r="C106" s="1">
         <f t="shared" si="12"/>
-        <v>2651.5467240335174</v>
+        <v>3389.8253940004734</v>
       </c>
       <c r="D106" s="1">
         <v>13</v>
       </c>
       <c r="E106" s="1">
         <f t="shared" si="13"/>
-        <v>3950</v>
+        <v>282</v>
       </c>
       <c r="F106" s="1">
         <f t="shared" si="14"/>
@@ -10657,28 +10851,28 @@
       </c>
       <c r="G106" s="1">
         <f t="shared" si="15"/>
-        <v>51350</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <f t="shared" si="10"/>
-        <v>2603.6799431009958</v>
+        <v>3344.8509683772841</v>
       </c>
       <c r="B107" s="1">
         <f t="shared" si="11"/>
-        <v>2627.858727265083</v>
+        <v>3367.5095071564538</v>
       </c>
       <c r="C107" s="1">
         <f t="shared" si="12"/>
-        <v>2652.0375114291705</v>
+        <v>3390.168045935623</v>
       </c>
       <c r="D107" s="1">
         <v>14</v>
       </c>
       <c r="E107" s="1">
         <f t="shared" si="13"/>
-        <v>1219</v>
+        <v>803</v>
       </c>
       <c r="F107" s="1">
         <f t="shared" si="14"/>
@@ -10686,28 +10880,28 @@
       </c>
       <c r="G107" s="1">
         <f t="shared" si="15"/>
-        <v>17066</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <f t="shared" si="10"/>
-        <v>2612.9630156472263</v>
+        <v>3353.4330889594044</v>
       </c>
       <c r="B108" s="1">
         <f t="shared" si="11"/>
-        <v>2632.7456572360252</v>
+        <v>3371.9718934150887</v>
       </c>
       <c r="C108" s="1">
         <f t="shared" si="12"/>
-        <v>2652.5282988248237</v>
+        <v>3390.5106978707731</v>
       </c>
       <c r="D108" s="1">
         <v>15</v>
       </c>
       <c r="E108" s="1">
         <f t="shared" si="13"/>
-        <v>5060</v>
+        <v>5316</v>
       </c>
       <c r="F108" s="1">
         <f t="shared" si="14"/>
@@ -10715,28 +10909,28 @@
       </c>
       <c r="G108" s="1">
         <f t="shared" si="15"/>
-        <v>75900</v>
+        <v>79740</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <f t="shared" si="10"/>
-        <v>2622.2460881934567</v>
+        <v>3362.0152095415251</v>
       </c>
       <c r="B109" s="1">
         <f t="shared" si="11"/>
-        <v>2637.6325872069665</v>
+        <v>3376.4342796737237</v>
       </c>
       <c r="C109" s="1">
         <f t="shared" si="12"/>
-        <v>2653.0190862204768</v>
+        <v>3390.8533498059228</v>
       </c>
       <c r="D109" s="1">
         <v>16</v>
       </c>
       <c r="E109" s="1">
         <f t="shared" si="13"/>
-        <v>4440</v>
+        <v>90</v>
       </c>
       <c r="F109" s="1">
         <f t="shared" si="14"/>
@@ -10744,28 +10938,28 @@
       </c>
       <c r="G109" s="1">
         <f t="shared" si="15"/>
-        <v>71040</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <f t="shared" si="10"/>
-        <v>2631.5291607396871</v>
+        <v>3370.5973301236459</v>
       </c>
       <c r="B110" s="1">
         <f t="shared" si="11"/>
-        <v>2642.5195171779087</v>
+        <v>3380.8966659323596</v>
       </c>
       <c r="C110" s="1">
         <f t="shared" si="12"/>
-        <v>2653.5098736161299</v>
+        <v>3391.1960017410729</v>
       </c>
       <c r="D110" s="1">
         <v>17</v>
       </c>
       <c r="E110" s="1">
         <f t="shared" si="13"/>
-        <v>3667</v>
+        <v>5873</v>
       </c>
       <c r="F110" s="1">
         <f t="shared" si="14"/>
@@ -10773,28 +10967,28 @@
       </c>
       <c r="G110" s="1">
         <f t="shared" si="15"/>
-        <v>62339</v>
+        <v>99841</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <f t="shared" si="10"/>
-        <v>2640.8122332859175</v>
+        <v>3379.1794507057662</v>
       </c>
       <c r="B111" s="1">
         <f t="shared" si="11"/>
-        <v>2647.4064471488505</v>
+        <v>3385.3590521909946</v>
       </c>
       <c r="C111" s="1">
         <f t="shared" si="12"/>
-        <v>2654.0006610117834</v>
+        <v>3391.5386536762226</v>
       </c>
       <c r="D111" s="1">
         <v>18</v>
       </c>
       <c r="E111" s="1">
         <f t="shared" si="13"/>
-        <v>751</v>
+        <v>345</v>
       </c>
       <c r="F111" s="1">
         <f t="shared" si="14"/>
@@ -10802,28 +10996,28 @@
       </c>
       <c r="G111" s="1">
         <f t="shared" si="15"/>
-        <v>13518</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <f t="shared" si="10"/>
-        <v>2650.0953058321479</v>
+        <v>3387.7615712878869</v>
       </c>
       <c r="B112" s="1">
         <f t="shared" si="11"/>
-        <v>2652.2933771197922</v>
+        <v>3389.8214384496296</v>
       </c>
       <c r="C112" s="1">
         <f t="shared" si="12"/>
-        <v>2654.4914484074366</v>
+        <v>3391.8813056113727</v>
       </c>
       <c r="D112" s="1">
         <v>19</v>
       </c>
       <c r="E112" s="1">
         <f t="shared" si="13"/>
-        <v>359</v>
+        <v>5374</v>
       </c>
       <c r="F112" s="1">
         <f t="shared" si="14"/>
@@ -10831,28 +11025,28 @@
       </c>
       <c r="G112" s="1">
         <f t="shared" si="15"/>
-        <v>6821</v>
+        <v>102106</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <f t="shared" si="10"/>
-        <v>2659.3783783783783</v>
+        <v>3396.3436918700077</v>
       </c>
       <c r="B113" s="1">
         <f t="shared" si="11"/>
-        <v>2657.180307090734</v>
+        <v>3394.283824708265</v>
       </c>
       <c r="C113" s="1">
         <f t="shared" si="12"/>
-        <v>2654.9822358030897</v>
+        <v>3392.2239575465223</v>
       </c>
       <c r="D113" s="1">
         <v>20</v>
       </c>
       <c r="E113" s="1">
         <f t="shared" si="13"/>
-        <v>4875</v>
+        <v>6486</v>
       </c>
       <c r="F113" s="1">
         <f t="shared" si="14"/>
@@ -10860,28 +11054,28 @@
       </c>
       <c r="G113" s="1">
         <f t="shared" si="15"/>
-        <v>97500</v>
+        <v>129720</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <f t="shared" si="10"/>
-        <v>2668.6614509246087</v>
+        <v>3404.925812452128</v>
       </c>
       <c r="B114" s="1">
         <f t="shared" si="11"/>
-        <v>2662.0672370616758</v>
+        <v>3398.7462109669004</v>
       </c>
       <c r="C114" s="1">
         <f t="shared" si="12"/>
-        <v>2655.4730231987428</v>
+        <v>3392.5666094816725</v>
       </c>
       <c r="D114" s="1">
         <v>21</v>
       </c>
       <c r="E114" s="1">
         <f t="shared" si="13"/>
-        <v>4832</v>
+        <v>6385</v>
       </c>
       <c r="F114" s="1">
         <f t="shared" si="14"/>
@@ -10889,28 +11083,28 @@
       </c>
       <c r="G114" s="1">
         <f t="shared" si="15"/>
-        <v>101472</v>
+        <v>134085</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <f t="shared" si="10"/>
-        <v>2677.9445234708392</v>
+        <v>3413.5079330342487</v>
       </c>
       <c r="B115" s="1">
         <f t="shared" si="11"/>
-        <v>2666.9541670326175</v>
+        <v>3403.2085972255354</v>
       </c>
       <c r="C115" s="1">
         <f t="shared" si="12"/>
-        <v>2655.9638105943959</v>
+        <v>3392.9092614168221</v>
       </c>
       <c r="D115" s="1">
         <v>22</v>
       </c>
       <c r="E115" s="1">
         <f t="shared" si="13"/>
-        <v>3700</v>
+        <v>6581</v>
       </c>
       <c r="F115" s="1">
         <f t="shared" si="14"/>
@@ -10918,28 +11112,28 @@
       </c>
       <c r="G115" s="1">
         <f t="shared" si="15"/>
-        <v>81400</v>
+        <v>144782</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <f t="shared" si="10"/>
-        <v>2687.2275960170696</v>
+        <v>3422.090053616369</v>
       </c>
       <c r="B116" s="1">
         <f t="shared" si="11"/>
-        <v>2671.8410970035593</v>
+        <v>3407.6709834841704</v>
       </c>
       <c r="C116" s="1">
         <f t="shared" si="12"/>
-        <v>2656.454597990049</v>
+        <v>3393.2519133519722</v>
       </c>
       <c r="D116" s="1">
         <v>23</v>
       </c>
       <c r="E116" s="1">
         <f t="shared" si="13"/>
-        <v>1589</v>
+        <v>6294</v>
       </c>
       <c r="F116" s="1">
         <f t="shared" si="14"/>
@@ -10947,28 +11141,28 @@
       </c>
       <c r="G116" s="1">
         <f t="shared" si="15"/>
-        <v>36547</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <f t="shared" si="10"/>
-        <v>2696.5106685633</v>
+        <v>3430.6721741984898</v>
       </c>
       <c r="B117" s="1">
         <f t="shared" si="11"/>
-        <v>2676.7280269745011</v>
+        <v>3412.1333697428058</v>
       </c>
       <c r="C117" s="1">
         <f t="shared" si="12"/>
-        <v>2656.9453853857021</v>
+        <v>3393.5945652871219</v>
       </c>
       <c r="D117" s="1">
         <v>24</v>
       </c>
       <c r="E117" s="1">
         <f t="shared" si="13"/>
-        <v>5017</v>
+        <v>5847</v>
       </c>
       <c r="F117" s="1">
         <f t="shared" si="14"/>
@@ -10976,28 +11170,28 @@
       </c>
       <c r="G117" s="1">
         <f t="shared" si="15"/>
-        <v>120408</v>
+        <v>140328</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f t="shared" si="10"/>
-        <v>2705.7937411095304</v>
+        <v>3439.2542947806105</v>
       </c>
       <c r="B118" s="1">
         <f t="shared" si="11"/>
-        <v>2681.6149569454428</v>
+        <v>3416.5957560014413</v>
       </c>
       <c r="C118" s="1">
         <f t="shared" si="12"/>
-        <v>2657.4361727813553</v>
+        <v>3393.937217222272</v>
       </c>
       <c r="D118" s="1">
         <v>25</v>
       </c>
       <c r="E118" s="1">
         <f t="shared" si="13"/>
-        <v>946</v>
+        <v>264</v>
       </c>
       <c r="F118" s="1">
         <f t="shared" si="14"/>
@@ -11005,28 +11199,28 @@
       </c>
       <c r="G118" s="1">
         <f t="shared" si="15"/>
-        <v>23650</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f t="shared" si="10"/>
-        <v>2715.0768136557608</v>
+        <v>3447.8364153627308</v>
       </c>
       <c r="B119" s="1">
         <f t="shared" si="11"/>
-        <v>2686.5018869163846</v>
+        <v>3421.0581422600762</v>
       </c>
       <c r="C119" s="1">
         <f t="shared" si="12"/>
-        <v>2657.9269601770084</v>
+        <v>3394.2798691574217</v>
       </c>
       <c r="D119" s="1">
         <v>26</v>
       </c>
       <c r="E119" s="1">
         <f t="shared" si="13"/>
-        <v>4646</v>
+        <v>989</v>
       </c>
       <c r="F119" s="1">
         <f t="shared" si="14"/>
@@ -11034,28 +11228,28 @@
       </c>
       <c r="G119" s="1">
         <f t="shared" si="15"/>
-        <v>120796</v>
+        <v>25714</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f t="shared" si="10"/>
-        <v>2724.3598862019917</v>
+        <v>3456.4185359448516</v>
       </c>
       <c r="B120" s="1">
         <f t="shared" si="11"/>
-        <v>2691.3888168873264</v>
+        <v>3425.5205285187112</v>
       </c>
       <c r="C120" s="1">
         <f t="shared" si="12"/>
-        <v>2658.4177475726615</v>
+        <v>3394.6225210925713</v>
       </c>
       <c r="D120" s="1">
         <v>27</v>
       </c>
       <c r="E120" s="1">
         <f t="shared" si="13"/>
-        <v>881</v>
+        <v>5725</v>
       </c>
       <c r="F120" s="1">
         <f t="shared" si="14"/>
@@ -11063,28 +11257,28 @@
       </c>
       <c r="G120" s="1">
         <f t="shared" si="15"/>
-        <v>23787</v>
+        <v>154575</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f t="shared" si="10"/>
-        <v>2733.6429587482221</v>
+        <v>3465.0006565269723</v>
       </c>
       <c r="B121" s="1">
         <f t="shared" si="11"/>
-        <v>2696.2757468582686</v>
+        <v>3429.9829147773471</v>
       </c>
       <c r="C121" s="1">
         <f t="shared" si="12"/>
-        <v>2658.9085349683146</v>
+        <v>3394.9651730277214</v>
       </c>
       <c r="D121" s="1">
         <v>28</v>
       </c>
       <c r="E121" s="1">
         <f t="shared" si="13"/>
-        <v>5342</v>
+        <v>294</v>
       </c>
       <c r="F121" s="1">
         <f t="shared" si="14"/>
@@ -11092,28 +11286,28 @@
       </c>
       <c r="G121" s="1">
         <f t="shared" si="15"/>
-        <v>149576</v>
+        <v>8232</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <f t="shared" si="10"/>
-        <v>2742.9260312944525</v>
+        <v>3473.5827771090926</v>
       </c>
       <c r="B122" s="1">
         <f t="shared" si="11"/>
-        <v>2701.1626768292103</v>
+        <v>3434.4453010359821</v>
       </c>
       <c r="C122" s="1">
         <f t="shared" si="12"/>
-        <v>2659.3993223639682</v>
+        <v>3395.3078249628711</v>
       </c>
       <c r="D122" s="1">
         <v>29</v>
       </c>
       <c r="E122" s="1">
         <f t="shared" si="13"/>
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="F122" s="1">
         <f t="shared" si="14"/>
@@ -11121,28 +11315,28 @@
       </c>
       <c r="G122" s="1">
         <f t="shared" si="15"/>
-        <v>7279</v>
+        <v>9715</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <f t="shared" si="10"/>
-        <v>2752.2091038406829</v>
+        <v>3482.1648976912134</v>
       </c>
       <c r="B123" s="1">
         <f t="shared" si="11"/>
-        <v>2706.0496068001521</v>
+        <v>3438.9076872946171</v>
       </c>
       <c r="C123" s="1">
         <f t="shared" si="12"/>
-        <v>2659.8901097596213</v>
+        <v>3395.6504768980212</v>
       </c>
       <c r="D123" s="1">
         <v>30</v>
       </c>
       <c r="E123" s="1">
         <f t="shared" si="13"/>
-        <v>576</v>
+        <v>6241</v>
       </c>
       <c r="F123" s="1">
         <f t="shared" si="14"/>
@@ -11150,28 +11344,28 @@
       </c>
       <c r="G123" s="1">
         <f t="shared" si="15"/>
-        <v>17280</v>
+        <v>187230</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <f t="shared" si="10"/>
-        <v>2761.4921763869133</v>
+        <v>3490.7470182733341</v>
       </c>
       <c r="B124" s="1">
         <f t="shared" si="11"/>
-        <v>2710.9365367710939</v>
+        <v>3443.3700735532525</v>
       </c>
       <c r="C124" s="1">
         <f t="shared" si="12"/>
-        <v>2660.3808971552744</v>
+        <v>3395.9931288331709</v>
       </c>
       <c r="D124" s="1">
         <v>31</v>
       </c>
       <c r="E124" s="1">
         <f t="shared" si="13"/>
-        <v>5157</v>
+        <v>5815</v>
       </c>
       <c r="F124" s="1">
         <f t="shared" si="14"/>
@@ -11179,28 +11373,28 @@
       </c>
       <c r="G124" s="1">
         <f t="shared" si="15"/>
-        <v>159867</v>
+        <v>180265</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <f t="shared" si="10"/>
-        <v>2770.7752489331438</v>
+        <v>3499.3291388554544</v>
       </c>
       <c r="B125" s="1">
         <f t="shared" si="11"/>
-        <v>2715.8234667420356</v>
+        <v>3447.8324598118879</v>
       </c>
       <c r="C125" s="1">
         <f t="shared" si="12"/>
-        <v>2660.8716845509275</v>
+        <v>3396.335780768321</v>
       </c>
       <c r="D125" s="1">
         <v>32</v>
       </c>
       <c r="E125" s="1">
         <f t="shared" si="13"/>
-        <v>4602</v>
+        <v>318</v>
       </c>
       <c r="F125" s="1">
         <f t="shared" si="14"/>
@@ -11208,28 +11402,28 @@
       </c>
       <c r="G125" s="1">
         <f t="shared" si="15"/>
-        <v>147264</v>
+        <v>10176</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <f t="shared" si="10"/>
-        <v>2780.0583214793742</v>
+        <v>3507.9112594375752</v>
       </c>
       <c r="B126" s="1">
         <f t="shared" si="11"/>
-        <v>2720.7103967129774</v>
+        <v>3452.2948460705229</v>
       </c>
       <c r="C126" s="1">
         <f t="shared" si="12"/>
-        <v>2661.3624719465806</v>
+        <v>3396.6784327034707</v>
       </c>
       <c r="D126" s="1">
         <v>33</v>
       </c>
       <c r="E126" s="1">
         <f t="shared" si="13"/>
-        <v>4254</v>
+        <v>5702</v>
       </c>
       <c r="F126" s="1">
         <f t="shared" si="14"/>
@@ -11237,28 +11431,28 @@
       </c>
       <c r="G126" s="1">
         <f t="shared" si="15"/>
-        <v>140382</v>
+        <v>188166</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f t="shared" si="10"/>
-        <v>2789.3413940256046</v>
+        <v>3516.4933800196955</v>
       </c>
       <c r="B127" s="1">
         <f t="shared" si="11"/>
-        <v>2725.5973266839192</v>
+        <v>3456.7572323291579</v>
       </c>
       <c r="C127" s="1">
         <f t="shared" si="12"/>
-        <v>2661.8532593422337</v>
+        <v>3397.0210846386208</v>
       </c>
       <c r="D127" s="1">
         <v>34</v>
       </c>
       <c r="E127" s="1">
         <f t="shared" si="13"/>
-        <v>1219</v>
+        <v>33</v>
       </c>
       <c r="F127" s="1">
         <f t="shared" si="14"/>
@@ -11266,28 +11460,28 @@
       </c>
       <c r="G127" s="1">
         <f t="shared" si="15"/>
-        <v>41446</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f t="shared" si="10"/>
-        <v>2798.624466571835</v>
+        <v>3525.0755006018162</v>
       </c>
       <c r="B128" s="1">
         <f t="shared" si="11"/>
-        <v>2730.4842566548609</v>
+        <v>3461.2196185877933</v>
       </c>
       <c r="C128" s="1">
         <f t="shared" si="12"/>
-        <v>2662.3440467378869</v>
+        <v>3397.3637365737704</v>
       </c>
       <c r="D128" s="1">
         <v>35</v>
       </c>
       <c r="E128" s="1">
         <f t="shared" si="13"/>
-        <v>5256</v>
+        <v>299</v>
       </c>
       <c r="F128" s="1">
         <f t="shared" si="14"/>
@@ -11295,28 +11489,28 @@
       </c>
       <c r="G128" s="1">
         <f t="shared" si="15"/>
-        <v>183960</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="10"/>
-        <v>2807.9075391180654</v>
+        <v>3533.657621183937</v>
       </c>
       <c r="B129" s="1">
         <f t="shared" si="11"/>
-        <v>2735.3711866258027</v>
+        <v>3465.6820048464288</v>
       </c>
       <c r="C129" s="1">
         <f t="shared" si="12"/>
-        <v>2662.83483413354</v>
+        <v>3397.7063885089206</v>
       </c>
       <c r="D129" s="1">
         <v>36</v>
       </c>
       <c r="E129" s="1">
         <f t="shared" si="13"/>
-        <v>685</v>
+        <v>6027</v>
       </c>
       <c r="F129" s="1">
         <f t="shared" si="14"/>
@@ -11324,28 +11518,28 @@
       </c>
       <c r="G129" s="1">
         <f t="shared" si="15"/>
-        <v>24660</v>
+        <v>216972</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="10"/>
-        <v>2817.1906116642958</v>
+        <v>3542.2397417660573</v>
       </c>
       <c r="B130" s="1">
         <f t="shared" si="11"/>
-        <v>2740.2581165967445</v>
+        <v>3470.1443911050637</v>
       </c>
       <c r="C130" s="1">
         <f t="shared" si="12"/>
-        <v>2663.3256215291931</v>
+        <v>3398.0490404440702</v>
       </c>
       <c r="D130" s="1">
         <v>37</v>
       </c>
       <c r="E130" s="1">
         <f t="shared" si="13"/>
-        <v>119</v>
+        <v>6527</v>
       </c>
       <c r="F130" s="1">
         <f t="shared" si="14"/>
@@ -11353,28 +11547,28 @@
       </c>
       <c r="G130" s="1">
         <f t="shared" si="15"/>
-        <v>4403</v>
+        <v>241499</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" si="10"/>
-        <v>2826.4736842105262</v>
+        <v>3550.821862348178</v>
       </c>
       <c r="B131" s="1">
         <f t="shared" si="11"/>
-        <v>2745.1450465676862</v>
+        <v>3474.6067773636992</v>
       </c>
       <c r="C131" s="1">
         <f t="shared" si="12"/>
-        <v>2663.8164089248462</v>
+        <v>3398.3916923792203</v>
       </c>
       <c r="D131" s="1">
         <v>38</v>
       </c>
       <c r="E131" s="1">
         <f t="shared" si="13"/>
-        <v>1001</v>
+        <v>1290</v>
       </c>
       <c r="F131" s="1">
         <f t="shared" si="14"/>
@@ -11382,12 +11576,12 @@
       </c>
       <c r="G131" s="1">
         <f t="shared" si="15"/>
-        <v>38038</v>
+        <v>49020</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N46:N83">
-    <sortCondition descending="1" ref="N46:N83"/>
+    <sortCondition descending="1" ref="N45:N83"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="J4:J42"/>
